--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,219 +400,219 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B2">
-        <v>12.406</v>
+        <v>5.03</v>
       </c>
       <c r="C2">
-        <v>0.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B3">
-        <v>2.231</v>
+        <v>6.46</v>
       </c>
       <c r="C3">
-        <v>0.748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B4">
-        <v>3.8</v>
+        <v>6.06</v>
       </c>
       <c r="C4">
-        <v>0.217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B5">
-        <v>3.092</v>
+        <v>6.7</v>
       </c>
       <c r="C5">
-        <v>0.457</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B6">
-        <v>17.412</v>
+        <v>4.033</v>
       </c>
       <c r="C6">
-        <v>0.018</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B7">
-        <v>24.545</v>
+        <v>4.554</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B8">
-        <v>30.145</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B9">
-        <v>14.545</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.104</v>
+        <v>5.492</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B10">
-        <v>6.692</v>
+        <v>1.178</v>
       </c>
       <c r="C10">
-        <v>0.099</v>
+        <v>1.095</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B11">
-        <v>12.518</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>5.116</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.762</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.004</v>
+        <v>7.466</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B13">
-        <v>10.892</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1.606</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B14">
-        <v>11.2</v>
+        <v>1.375</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1.148</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B15">
-        <v>11.882</v>
+        <v>0.349</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2.308</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.459</v>
+        <v>0.846</v>
       </c>
       <c r="C16">
-        <v>1.39</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>4.762</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>4.133</v>
       </c>
       <c r="C18">
-        <v>2.983</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>12.826</v>
       </c>
       <c r="C19">
-        <v>2.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B20">
-        <v>15.189</v>
+        <v>12.97</v>
       </c>
       <c r="C20">
-        <v>0.124</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B21">
-        <v>11.738</v>
+        <v>25.53</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,21 +620,21 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B22">
-        <v>23.345</v>
+        <v>8.823</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B23">
-        <v>23.495</v>
+        <v>16.255</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -642,210 +642,122 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B24">
-        <v>15.371</v>
+        <v>4.238</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B25">
-        <v>22.128</v>
+        <v>1.698</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B26">
-        <v>3.152</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.331</v>
+        <v>9.161</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B27">
-        <v>31.594</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>19.203</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B28">
-        <v>48.481</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>7.941</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B29">
-        <v>40.719</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>6.935</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B30">
-        <v>46.416</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>24.514</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B31">
-        <v>6.198</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.407</v>
+        <v>16.716</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>1.22</v>
+        <v>12.953</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.141</v>
+        <v>17.269</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.186</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.975</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
-        <v>46079.34375</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
-        <v>46079.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>1.118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
-        <v>46079.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0.464</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46079.375</v>
-      </c>
-      <c r="B38">
-        <v>7.07</v>
-      </c>
-      <c r="C38">
-        <v>0.533</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46079.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>17.821</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46079.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>4.435</v>
-      </c>
-      <c r="C40">
-        <v>0.136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46079.40625</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0.508</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46079.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,21 +400,21 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B2">
-        <v>5.03</v>
+        <v>12.682</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B3">
-        <v>6.46</v>
+        <v>7.588</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -422,10 +422,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B4">
-        <v>6.06</v>
+        <v>20.682</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -433,164 +433,164 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B5">
-        <v>6.7</v>
+        <v>13.615</v>
       </c>
       <c r="C5">
-        <v>0.229</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B6">
-        <v>4.033</v>
+        <v>13.041</v>
       </c>
       <c r="C6">
-        <v>0.361</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B7">
-        <v>4.554</v>
+        <v>5.611</v>
       </c>
       <c r="C7">
-        <v>0.008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0.525</v>
       </c>
       <c r="C8">
-        <v>0.993</v>
+        <v>2.997</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="C9">
-        <v>5.492</v>
+        <v>3.589</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.178</v>
+        <v>4.436</v>
       </c>
       <c r="C10">
-        <v>1.095</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>3.598</v>
       </c>
       <c r="C11">
-        <v>5.116</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="C12">
-        <v>7.466</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="C13">
-        <v>1.606</v>
+        <v>7.651</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B14">
-        <v>1.375</v>
+        <v>2.37</v>
       </c>
       <c r="C14">
-        <v>1.148</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.349</v>
+        <v>6.828</v>
       </c>
       <c r="C15">
-        <v>2.308</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.846</v>
+        <v>31.139</v>
       </c>
       <c r="C16">
-        <v>0.753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>24.277</v>
       </c>
       <c r="C17">
-        <v>0.664</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B18">
-        <v>4.133</v>
+        <v>6.099</v>
       </c>
       <c r="C18">
-        <v>0.076</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B19">
-        <v>12.826</v>
+        <v>10.2</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,21 +598,21 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B20">
-        <v>12.97</v>
+        <v>13.709</v>
       </c>
       <c r="C20">
-        <v>0.007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B21">
-        <v>25.53</v>
+        <v>9.962</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,144 +620,155 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B22">
-        <v>8.823</v>
+        <v>1.179</v>
       </c>
       <c r="C22">
-        <v>0.378</v>
+        <v>7.723</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B23">
-        <v>16.255</v>
+        <v>0.636</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B24">
-        <v>4.238</v>
+        <v>2.241</v>
       </c>
       <c r="C24">
-        <v>0.138</v>
+        <v>2.111</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.698</v>
+        <v>2.672</v>
       </c>
       <c r="C25">
-        <v>0.874</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>1.437</v>
       </c>
       <c r="C26">
-        <v>9.161</v>
+        <v>1.912</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>12.85</v>
       </c>
       <c r="C27">
-        <v>19.203</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>34.92</v>
       </c>
       <c r="C28">
-        <v>7.941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>54.234</v>
       </c>
       <c r="C29">
-        <v>6.935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>70.569</v>
       </c>
       <c r="C30">
-        <v>24.514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>27.116</v>
       </c>
       <c r="C31">
-        <v>16.716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>67.759</v>
       </c>
       <c r="C32">
-        <v>12.953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>33.954</v>
       </c>
       <c r="C33">
-        <v>17.269</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>25.009</v>
       </c>
       <c r="C34">
+        <v>0.358</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>46107.35416666666</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,21 +400,21 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B2">
-        <v>12.682</v>
+        <v>21.014</v>
       </c>
       <c r="C2">
-        <v>0.036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46107.01041666666</v>
+        <v>46108.01041666666</v>
       </c>
       <c r="B3">
-        <v>7.588</v>
+        <v>17.948</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -422,10 +422,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46107.02083333334</v>
+        <v>46108.02083333334</v>
       </c>
       <c r="B4">
-        <v>20.682</v>
+        <v>21.04</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -433,131 +433,131 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46107.03125</v>
+        <v>46108.03125</v>
       </c>
       <c r="B5">
-        <v>13.615</v>
+        <v>13.24</v>
       </c>
       <c r="C5">
-        <v>0.109</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46107.04166666666</v>
+        <v>46108.04166666666</v>
       </c>
       <c r="B6">
-        <v>13.041</v>
+        <v>3.512</v>
       </c>
       <c r="C6">
-        <v>0.122</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46107.05208333334</v>
+        <v>46108.05208333334</v>
       </c>
       <c r="B7">
-        <v>5.611</v>
+        <v>1.522</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46107.0625</v>
+        <v>46108.0625</v>
       </c>
       <c r="B8">
-        <v>0.525</v>
+        <v>10.475</v>
       </c>
       <c r="C8">
-        <v>2.997</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46107.07291666666</v>
+        <v>46108.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.237</v>
+        <v>14.856</v>
       </c>
       <c r="C9">
-        <v>3.589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46107.08333333334</v>
+        <v>46108.08333333334</v>
       </c>
       <c r="B10">
-        <v>4.436</v>
+        <v>7.082</v>
       </c>
       <c r="C10">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46107.09375</v>
+        <v>46108.09375</v>
       </c>
       <c r="B11">
-        <v>3.598</v>
+        <v>17.167</v>
       </c>
       <c r="C11">
-        <v>0.681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46107.10416666666</v>
+        <v>46108.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.073</v>
+        <v>18.209</v>
       </c>
       <c r="C12">
-        <v>10.258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46107.11458333334</v>
+        <v>46108.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.236</v>
+        <v>15.6</v>
       </c>
       <c r="C13">
-        <v>7.651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46107.125</v>
+        <v>46108.125</v>
       </c>
       <c r="B14">
-        <v>2.37</v>
+        <v>24.555</v>
       </c>
       <c r="C14">
-        <v>0.431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46107.13541666666</v>
+        <v>46108.13541666666</v>
       </c>
       <c r="B15">
-        <v>6.828</v>
+        <v>44.213</v>
       </c>
       <c r="C15">
-        <v>0.044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46107.14583333334</v>
+        <v>46108.14583333334</v>
       </c>
       <c r="B16">
-        <v>31.139</v>
+        <v>28.061</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -565,32 +565,32 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46107.15625</v>
+        <v>46108.15625</v>
       </c>
       <c r="B17">
-        <v>24.277</v>
+        <v>39.315</v>
       </c>
       <c r="C17">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46107.16666666666</v>
+        <v>46108.16666666666</v>
       </c>
       <c r="B18">
-        <v>6.099</v>
+        <v>10.987</v>
       </c>
       <c r="C18">
-        <v>0.056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46107.17708333334</v>
+        <v>46108.17708333334</v>
       </c>
       <c r="B19">
-        <v>10.2</v>
+        <v>3.365</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,10 +598,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46107.1875</v>
+        <v>46108.1875</v>
       </c>
       <c r="B20">
-        <v>13.709</v>
+        <v>21.747</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46107.19791666666</v>
+        <v>46108.19791666666</v>
       </c>
       <c r="B21">
-        <v>9.962</v>
+        <v>29.191</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,98 +620,98 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46107.20833333334</v>
+        <v>46108.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.179</v>
+        <v>18.381</v>
       </c>
       <c r="C22">
-        <v>7.723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46107.21875</v>
+        <v>46108.21875</v>
       </c>
       <c r="B23">
-        <v>0.636</v>
+        <v>24.686</v>
       </c>
       <c r="C23">
-        <v>2.444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46107.22916666666</v>
+        <v>46108.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.241</v>
+        <v>11.428</v>
       </c>
       <c r="C24">
-        <v>2.111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46107.23958333334</v>
+        <v>46108.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.672</v>
+        <v>18.328</v>
       </c>
       <c r="C25">
-        <v>0.583</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46107.25</v>
+        <v>46108.25</v>
       </c>
       <c r="B26">
-        <v>1.437</v>
+        <v>0.472</v>
       </c>
       <c r="C26">
-        <v>1.912</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46107.26041666666</v>
+        <v>46108.26041666666</v>
       </c>
       <c r="B27">
-        <v>12.85</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.008999999999999999</v>
+        <v>2.068</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46107.27083333334</v>
+        <v>46108.27083333334</v>
       </c>
       <c r="B28">
-        <v>34.92</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1.902</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46107.28125</v>
+        <v>46108.28125</v>
       </c>
       <c r="B29">
-        <v>54.234</v>
+        <v>1.201</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46107.29166666666</v>
+        <v>46108.29166666666</v>
       </c>
       <c r="B30">
-        <v>70.569</v>
+        <v>25.734</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -719,56 +719,89 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46107.30208333334</v>
+        <v>46108.30208333334</v>
       </c>
       <c r="B31">
-        <v>27.116</v>
+        <v>0.023</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>4.421</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46107.3125</v>
+        <v>46108.3125</v>
       </c>
       <c r="B32">
-        <v>67.759</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>5.168</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46107.32291666666</v>
+        <v>46108.32291666666</v>
       </c>
       <c r="B33">
-        <v>33.954</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.372</v>
+        <v>9.225</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46107.33333333334</v>
+        <v>46108.33333333334</v>
       </c>
       <c r="B34">
-        <v>25.009</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.358</v>
+        <v>16.722</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46107.35416666666</v>
+        <v>46108.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
+        <v>31.469</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>46108.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>22.427</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>46108.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>0.178</v>
+      </c>
+      <c r="C37">
+        <v>8.183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>46108.375</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,153 +400,153 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B2">
-        <v>21.014</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>22.996</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46108.01041666666</v>
+        <v>46111.01041666666</v>
       </c>
       <c r="B3">
-        <v>17.948</v>
+        <v>0.002</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>12.405</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46108.02083333334</v>
+        <v>46111.02083333334</v>
       </c>
       <c r="B4">
-        <v>21.04</v>
+        <v>4.059</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46108.03125</v>
+        <v>46111.03125</v>
       </c>
       <c r="B5">
-        <v>13.24</v>
+        <v>3.482</v>
       </c>
       <c r="C5">
-        <v>0.455</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46108.04166666666</v>
+        <v>46111.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.512</v>
+        <v>3.484</v>
       </c>
       <c r="C6">
-        <v>0.8090000000000001</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46108.05208333334</v>
+        <v>46111.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.522</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.216</v>
+        <v>11.777</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46108.0625</v>
+        <v>46111.0625</v>
       </c>
       <c r="B8">
-        <v>10.475</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.06900000000000001</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46108.07291666666</v>
+        <v>46111.07291666666</v>
       </c>
       <c r="B9">
-        <v>14.856</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2.486</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46108.08333333334</v>
+        <v>46111.08333333334</v>
       </c>
       <c r="B10">
-        <v>7.082</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>11.504</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46108.09375</v>
+        <v>46111.09375</v>
       </c>
       <c r="B11">
-        <v>17.167</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>17.615</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46108.10416666666</v>
+        <v>46111.10416666666</v>
       </c>
       <c r="B12">
-        <v>18.209</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>17.991</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46108.11458333334</v>
+        <v>46111.11458333334</v>
       </c>
       <c r="B13">
-        <v>15.6</v>
+        <v>6.461</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46108.125</v>
+        <v>46111.125</v>
       </c>
       <c r="B14">
-        <v>24.555</v>
+        <v>13.831</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46108.13541666666</v>
+        <v>46111.13541666666</v>
       </c>
       <c r="B15">
-        <v>44.213</v>
+        <v>16.832</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -554,10 +554,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46108.14583333334</v>
+        <v>46111.14583333334</v>
       </c>
       <c r="B16">
-        <v>28.061</v>
+        <v>28.288</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -565,10 +565,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46108.15625</v>
+        <v>46111.15625</v>
       </c>
       <c r="B17">
-        <v>39.315</v>
+        <v>13.641</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -576,10 +576,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46108.16666666666</v>
+        <v>46111.16666666666</v>
       </c>
       <c r="B18">
-        <v>10.987</v>
+        <v>12.742</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -587,10 +587,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46108.17708333334</v>
+        <v>46111.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.365</v>
+        <v>11.6</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,10 +598,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46108.1875</v>
+        <v>46111.1875</v>
       </c>
       <c r="B20">
-        <v>21.747</v>
+        <v>27.185</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46108.19791666666</v>
+        <v>46111.19791666666</v>
       </c>
       <c r="B21">
-        <v>29.191</v>
+        <v>25.729</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,21 +620,21 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46108.20833333334</v>
+        <v>46111.20833333334</v>
       </c>
       <c r="B22">
-        <v>18.381</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1.958</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46108.21875</v>
+        <v>46111.21875</v>
       </c>
       <c r="B23">
-        <v>24.686</v>
+        <v>3.008</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -642,166 +642,111 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46108.22916666666</v>
+        <v>46111.22916666666</v>
       </c>
       <c r="B24">
-        <v>11.428</v>
+        <v>3.839</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46108.23958333334</v>
+        <v>46111.23958333334</v>
       </c>
       <c r="B25">
-        <v>18.328</v>
+        <v>11.051</v>
       </c>
       <c r="C25">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46108.25</v>
+        <v>46111.25</v>
       </c>
       <c r="B26">
-        <v>0.472</v>
+        <v>0.907</v>
       </c>
       <c r="C26">
-        <v>1.79</v>
+        <v>5.739</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46108.26041666666</v>
+        <v>46111.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="C27">
-        <v>2.068</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46108.27083333334</v>
+        <v>46111.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>5.304</v>
       </c>
       <c r="C28">
-        <v>1.902</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46108.28125</v>
+        <v>46111.28125</v>
       </c>
       <c r="B29">
-        <v>1.201</v>
+        <v>22.522</v>
       </c>
       <c r="C29">
-        <v>0.411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46108.29166666666</v>
+        <v>46111.29166666666</v>
       </c>
       <c r="B30">
-        <v>25.734</v>
+        <v>2.255</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>42.907</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46108.30208333334</v>
+        <v>46111.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>4.421</v>
+        <v>59.517</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46108.3125</v>
+        <v>46111.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C32">
-        <v>5.168</v>
+        <v>19.635</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46108.32291666666</v>
+        <v>46111.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>9.225</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2">
-        <v>46108.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>16.722</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
-        <v>46108.34375</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>31.469</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
-        <v>46108.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>22.427</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
-        <v>46108.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>0.178</v>
-      </c>
-      <c r="C37">
-        <v>8.183</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46108.375</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,353 +400,584 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2.231</v>
       </c>
       <c r="C2">
-        <v>22.996</v>
+        <v>2.764</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46111.01041666666</v>
+        <v>46115.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.002</v>
+        <v>0.723</v>
       </c>
       <c r="C3">
-        <v>12.405</v>
+        <v>7.332</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46111.02083333334</v>
+        <v>46115.02083333334</v>
       </c>
       <c r="B4">
-        <v>4.059</v>
+        <v>0.419</v>
       </c>
       <c r="C4">
-        <v>0.409</v>
+        <v>6.676</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46111.03125</v>
+        <v>46115.03125</v>
       </c>
       <c r="B5">
-        <v>3.482</v>
+        <v>0.066</v>
       </c>
       <c r="C5">
-        <v>0.602</v>
+        <v>10.602</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46111.04166666666</v>
+        <v>46115.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.484</v>
+        <v>0.305</v>
       </c>
       <c r="C6">
-        <v>0.721</v>
+        <v>4.869</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46111.05208333334</v>
+        <v>46115.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>7.429</v>
       </c>
       <c r="C7">
-        <v>11.777</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46111.0625</v>
+        <v>46115.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>7.71</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46111.07291666666</v>
+        <v>46115.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C9">
-        <v>2.486</v>
+        <v>2.753</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46111.08333333334</v>
+        <v>46115.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="C10">
-        <v>11.504</v>
+        <v>3.204</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46111.09375</v>
+        <v>46115.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1.604</v>
       </c>
       <c r="C11">
-        <v>17.615</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46111.10416666666</v>
+        <v>46115.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>7.624</v>
       </c>
       <c r="C12">
-        <v>17.991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46111.11458333334</v>
+        <v>46115.11458333334</v>
       </c>
       <c r="B13">
-        <v>6.461</v>
+        <v>8.92</v>
       </c>
       <c r="C13">
-        <v>0.569</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46111.125</v>
+        <v>46115.125</v>
       </c>
       <c r="B14">
-        <v>13.831</v>
+        <v>2.397</v>
       </c>
       <c r="C14">
-        <v>0.074</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46111.13541666666</v>
+        <v>46115.13541666666</v>
       </c>
       <c r="B15">
-        <v>16.832</v>
+        <v>0.4</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46111.14583333334</v>
+        <v>46115.14583333334</v>
       </c>
       <c r="B16">
-        <v>28.288</v>
+        <v>3.016</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46111.15625</v>
+        <v>46115.15625</v>
       </c>
       <c r="B17">
-        <v>13.641</v>
+        <v>2.153</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46111.16666666666</v>
+        <v>46115.16666666666</v>
       </c>
       <c r="B18">
-        <v>12.742</v>
+        <v>0.121</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>4.738</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46111.17708333334</v>
+        <v>46115.17708333334</v>
       </c>
       <c r="B19">
-        <v>11.6</v>
+        <v>0.727</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46111.1875</v>
+        <v>46115.1875</v>
       </c>
       <c r="B20">
-        <v>27.185</v>
+        <v>2.378</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46111.19791666666</v>
+        <v>46115.19791666666</v>
       </c>
       <c r="B21">
-        <v>25.729</v>
+        <v>0.167</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>3.991</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46111.20833333334</v>
+        <v>46115.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.5659999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="C22">
-        <v>1.958</v>
+        <v>7.737</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46111.21875</v>
+        <v>46115.21875</v>
       </c>
       <c r="B23">
-        <v>3.008</v>
+        <v>0.528</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>6.292</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46111.22916666666</v>
+        <v>46115.22916666666</v>
       </c>
       <c r="B24">
-        <v>3.839</v>
+        <v>0.185</v>
       </c>
       <c r="C24">
-        <v>0.18</v>
+        <v>5.737</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46111.23958333334</v>
+        <v>46115.23958333334</v>
       </c>
       <c r="B25">
-        <v>11.051</v>
+        <v>1.388</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1.719</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46111.25</v>
+        <v>46115.25</v>
       </c>
       <c r="B26">
-        <v>0.907</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C26">
-        <v>5.739</v>
+        <v>46.609</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46111.26041666666</v>
+        <v>46115.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.373</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>6.53</v>
+        <v>30.636</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46111.27083333334</v>
+        <v>46115.27083333334</v>
       </c>
       <c r="B28">
-        <v>5.304</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.585</v>
+        <v>21.996</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46111.28125</v>
+        <v>46115.28125</v>
       </c>
       <c r="B29">
-        <v>22.522</v>
+        <v>0.433</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>7.352</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46111.29166666666</v>
+        <v>46115.29166666666</v>
       </c>
       <c r="B30">
-        <v>2.255</v>
+        <v>0.63</v>
       </c>
       <c r="C30">
-        <v>42.907</v>
+        <v>4.129</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46111.30208333334</v>
+        <v>46115.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="C31">
-        <v>59.517</v>
+        <v>5.545</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46111.3125</v>
+        <v>46115.3125</v>
       </c>
       <c r="B32">
-        <v>0.08400000000000001</v>
+        <v>1.048</v>
       </c>
       <c r="C32">
-        <v>19.635</v>
+        <v>5.273</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46111.32291666666</v>
+        <v>46115.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>3.331</v>
       </c>
       <c r="C33">
+        <v>4.165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2">
+        <v>46115.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>4.186</v>
+      </c>
+      <c r="C34">
+        <v>1.696</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>46115.34375</v>
+      </c>
+      <c r="B35">
+        <v>0.216</v>
+      </c>
+      <c r="C35">
+        <v>6.195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>46115.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>14.243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>46115.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>4.038</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>46115.375</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>7.334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>46115.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>11.893</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46115.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>20.238</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46115.40625</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>2.141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46115.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>1.569</v>
+      </c>
+      <c r="C42">
+        <v>1.847</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46115.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>8.161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46115.4375</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>7.503</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46115.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0.133</v>
+      </c>
+      <c r="C45">
+        <v>9.018000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46115.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>1.321</v>
+      </c>
+      <c r="C46">
+        <v>0.906</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46115.46875</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>13.756</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46115.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>31.296</v>
+      </c>
+      <c r="C48">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46115.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>7.375</v>
+      </c>
+      <c r="C49">
+        <v>0.282</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46115.5</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>12.417</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46115.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0.147</v>
+      </c>
+      <c r="C51">
+        <v>8.962</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46115.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0.215</v>
+      </c>
+      <c r="C52">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46115.53125</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>7.091</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46115.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,584 +400,573 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B2">
-        <v>2.231</v>
+        <v>3.011</v>
       </c>
       <c r="C2">
-        <v>2.764</v>
+        <v>1.759</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46115.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.723</v>
+        <v>1.775</v>
       </c>
       <c r="C3">
-        <v>7.332</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46115.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.419</v>
+        <v>0.627</v>
       </c>
       <c r="C4">
-        <v>6.676</v>
+        <v>4.227</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46115.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
-        <v>0.066</v>
+        <v>5.656</v>
       </c>
       <c r="C5">
-        <v>10.602</v>
+        <v>1.861</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46115.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.305</v>
+        <v>0.831</v>
       </c>
       <c r="C6">
-        <v>4.869</v>
+        <v>2.642</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46115.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>7.429</v>
+        <v>1.457</v>
       </c>
       <c r="C7">
-        <v>0.416</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46115.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="C8">
-        <v>0.64</v>
+        <v>6.735</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46115.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>2.753</v>
+        <v>1.658</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46115.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>3.204</v>
+        <v>19.173</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46115.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
-        <v>1.604</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.143</v>
+        <v>7.988</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46115.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
-        <v>7.624</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>9.202999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46115.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
-        <v>8.92</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.021</v>
+        <v>9.012</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46115.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
-        <v>2.397</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0.205</v>
+        <v>22.153</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46115.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>1.18</v>
+        <v>26.186</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46115.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.016</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0.025</v>
+        <v>14.695</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46115.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>2.153</v>
+        <v>1.741</v>
       </c>
       <c r="C17">
-        <v>0.191</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46115.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.121</v>
+        <v>0.216</v>
       </c>
       <c r="C18">
-        <v>4.738</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46115.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.727</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1.31</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46115.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>2.378</v>
+        <v>2.616</v>
       </c>
       <c r="C20">
-        <v>0.226</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46115.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.167</v>
+        <v>7.47</v>
       </c>
       <c r="C21">
-        <v>3.991</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46115.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="C22">
-        <v>7.737</v>
+        <v>11.005</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46115.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>6.292</v>
+        <v>6.067</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46115.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>5.737</v>
+        <v>16.866</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46115.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.388</v>
+        <v>1.766</v>
       </c>
       <c r="C25">
-        <v>1.719</v>
+        <v>10.572</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46115.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>0.08599999999999999</v>
+        <v>1.955</v>
       </c>
       <c r="C26">
-        <v>46.609</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46115.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>23.412</v>
       </c>
       <c r="C27">
-        <v>30.636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46115.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>4.449</v>
       </c>
       <c r="C28">
-        <v>21.996</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46115.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>0.433</v>
+        <v>3.862</v>
       </c>
       <c r="C29">
-        <v>7.352</v>
+        <v>2.234</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46115.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>4.129</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46115.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.713</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>5.545</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46115.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>5.273</v>
+        <v>8.765000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46115.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>3.331</v>
+        <v>0.293</v>
       </c>
       <c r="C33">
-        <v>4.165</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46115.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>4.186</v>
+        <v>0.424</v>
       </c>
       <c r="C34">
-        <v>1.696</v>
+        <v>3.967</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46115.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>0.216</v>
+        <v>4.472</v>
       </c>
       <c r="C35">
-        <v>6.195</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46115.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>14.243</v>
+        <v>8.827999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46115.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>4.038</v>
+        <v>4.544</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46115.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>6.674</v>
       </c>
       <c r="C38">
-        <v>7.334</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46115.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="C39">
-        <v>11.893</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46115.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>20.238</v>
+        <v>6.953</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46115.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>2.141</v>
+        <v>12.491</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46115.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>1.569</v>
+        <v>0.007</v>
       </c>
       <c r="C42">
-        <v>1.847</v>
+        <v>14.298</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46115.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C43">
-        <v>8.161</v>
+        <v>3.399</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46115.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2.393</v>
       </c>
       <c r="C44">
-        <v>7.503</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46115.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.133</v>
+        <v>0.532</v>
       </c>
       <c r="C45">
-        <v>9.018000000000001</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46115.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>1.321</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>0.906</v>
+        <v>6.487</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46115.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>6.315</v>
       </c>
       <c r="C47">
-        <v>13.756</v>
+        <v>1.294</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46115.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>31.296</v>
+        <v>1.28</v>
       </c>
       <c r="C48">
-        <v>0.001</v>
+        <v>4.945</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>46115.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>7.375</v>
+        <v>0.421</v>
       </c>
       <c r="C49">
-        <v>0.282</v>
+        <v>16.301</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2">
-        <v>46115.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>12.417</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2">
-        <v>46115.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>8.962</v>
+        <v>2.661</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2">
-        <v>46115.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.215</v>
+        <v>0.181</v>
       </c>
       <c r="C52">
-        <v>1.89</v>
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2">
-        <v>46115.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>7.091</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46115.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,573 +400,364 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B2">
-        <v>3.011</v>
+        <v>1.546</v>
       </c>
       <c r="C2">
-        <v>1.759</v>
+        <v>2.201</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46129.01041666666</v>
+        <v>46132.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.775</v>
+        <v>5.65</v>
       </c>
       <c r="C3">
-        <v>1.111</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46129.02083333334</v>
+        <v>46132.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.627</v>
+        <v>0.176</v>
       </c>
       <c r="C4">
-        <v>4.227</v>
+        <v>1.706</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46129.03125</v>
+        <v>46132.03125</v>
       </c>
       <c r="B5">
-        <v>5.656</v>
+        <v>0.258</v>
       </c>
       <c r="C5">
-        <v>1.861</v>
+        <v>1.211</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46129.04166666666</v>
+        <v>46132.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.831</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2.642</v>
+        <v>23.034</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46129.05208333334</v>
+        <v>46132.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.457</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1.701</v>
+        <v>32.834</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46129.0625</v>
+        <v>46132.0625</v>
       </c>
       <c r="B8">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>6.735</v>
+        <v>35.12</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46129.07291666666</v>
+        <v>46132.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="C9">
-        <v>1.658</v>
+        <v>5.431</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46129.08333333334</v>
+        <v>46132.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="C10">
-        <v>19.173</v>
+        <v>1.574</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46129.09375</v>
+        <v>46132.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>11.032</v>
       </c>
       <c r="C11">
-        <v>7.988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46129.10416666666</v>
+        <v>46132.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1.748</v>
       </c>
       <c r="C12">
-        <v>9.202999999999999</v>
+        <v>2.375</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46129.11458333334</v>
+        <v>46132.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>9.012</v>
+        <v>3.013</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46129.125</v>
+        <v>46132.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>22.153</v>
+        <v>8.936999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46129.13541666666</v>
+        <v>46132.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>26.186</v>
+        <v>11.604</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46129.14583333334</v>
+        <v>46132.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C16">
-        <v>14.695</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46129.15625</v>
+        <v>46132.15625</v>
       </c>
       <c r="B17">
-        <v>1.741</v>
+        <v>1.095</v>
       </c>
       <c r="C17">
-        <v>0.512</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46129.16666666666</v>
+        <v>46132.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.216</v>
+        <v>5.197</v>
       </c>
       <c r="C18">
-        <v>0.136</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46129.17708333334</v>
+        <v>46132.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1.512</v>
       </c>
       <c r="C19">
-        <v>0.156</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46129.1875</v>
+        <v>46132.1875</v>
       </c>
       <c r="B20">
-        <v>2.616</v>
+        <v>1.813</v>
       </c>
       <c r="C20">
-        <v>1.858</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46129.19791666666</v>
+        <v>46132.19791666666</v>
       </c>
       <c r="B21">
-        <v>7.47</v>
+        <v>4.089</v>
       </c>
       <c r="C21">
-        <v>0.459</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46129.20833333334</v>
+        <v>46132.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.01</v>
+        <v>1.082</v>
       </c>
       <c r="C22">
-        <v>11.005</v>
+        <v>13.109</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46129.21875</v>
+        <v>46132.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2.264</v>
       </c>
       <c r="C23">
-        <v>6.067</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46129.22916666666</v>
+        <v>46132.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>4.878</v>
       </c>
       <c r="C24">
-        <v>16.866</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46129.23958333334</v>
+        <v>46132.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.766</v>
+        <v>12.757</v>
       </c>
       <c r="C25">
-        <v>10.572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46129.25</v>
+        <v>46132.25</v>
       </c>
       <c r="B26">
-        <v>1.955</v>
+        <v>0.881</v>
       </c>
       <c r="C26">
-        <v>0.294</v>
+        <v>7.377</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46129.26041666666</v>
+        <v>46132.26041666666</v>
       </c>
       <c r="B27">
-        <v>23.412</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>9.622999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46129.27083333334</v>
+        <v>46132.27083333334</v>
       </c>
       <c r="B28">
-        <v>4.449</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.668</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46129.28125</v>
+        <v>46132.28125</v>
       </c>
       <c r="B29">
-        <v>3.862</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>2.234</v>
+        <v>26.048</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46129.29166666666</v>
+        <v>46132.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>12.408</v>
+        <v>4.891</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46129.30208333334</v>
+        <v>46132.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>4.73</v>
+        <v>6.584</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46129.3125</v>
+        <v>46132.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>8.765000000000001</v>
+        <v>4.244</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46129.32291666666</v>
+        <v>46132.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.293</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>2.708</v>
+        <v>7.994</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46129.33333333334</v>
+        <v>46132.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>3.967</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
-        <v>46129.34375</v>
-      </c>
-      <c r="B35">
-        <v>4.472</v>
-      </c>
-      <c r="C35">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
-        <v>46129.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>8.827999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
-        <v>46129.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>4.544</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46129.375</v>
-      </c>
-      <c r="B38">
-        <v>6.674</v>
-      </c>
-      <c r="C38">
-        <v>0.259</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46129.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>3.333</v>
-      </c>
-      <c r="C39">
-        <v>0.978</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46129.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>6.953</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46129.40625</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>12.491</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46129.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>0.007</v>
-      </c>
-      <c r="C42">
-        <v>14.298</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46129.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0.01</v>
-      </c>
-      <c r="C43">
-        <v>3.399</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46129.4375</v>
-      </c>
-      <c r="B44">
-        <v>2.393</v>
-      </c>
-      <c r="C44">
-        <v>0.347</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46129.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>0.532</v>
-      </c>
-      <c r="C45">
-        <v>4.84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46129.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>6.487</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46129.46875</v>
-      </c>
-      <c r="B47">
-        <v>6.315</v>
-      </c>
-      <c r="C47">
-        <v>1.294</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46129.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>1.28</v>
-      </c>
-      <c r="C48">
-        <v>4.945</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46129.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>0.421</v>
-      </c>
-      <c r="C49">
-        <v>16.301</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46129.5</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50">
-        <v>2.507</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46129.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>2.661</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46129.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0.181</v>
-      </c>
-      <c r="C52">
-        <v>0.5679999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46129.53125</v>
-      </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,109 +400,109 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
-        <v>1.546</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>2.201</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.006</v>
+        <v>41.326</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1.706</v>
+        <v>32.276</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1.211</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>23.034</v>
+        <v>51.713</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>32.834</v>
+        <v>90.974</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>35.12</v>
+        <v>37.539</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.728</v>
+        <v>0.232</v>
       </c>
       <c r="C9">
-        <v>5.431</v>
+        <v>3.134</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="C10">
-        <v>1.574</v>
+        <v>5.875</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>11.032</v>
+        <v>19.015</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -510,254 +510,353 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.748</v>
+        <v>6.204</v>
       </c>
       <c r="C12">
-        <v>2.375</v>
+        <v>4.984</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>10.306</v>
       </c>
       <c r="C13">
-        <v>3.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>3.963</v>
       </c>
       <c r="C14">
-        <v>8.936999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="C15">
-        <v>11.604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.017</v>
+        <v>11.435</v>
       </c>
       <c r="C16">
-        <v>6.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>1.095</v>
+        <v>2.24</v>
       </c>
       <c r="C17">
-        <v>0.363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>5.197</v>
+        <v>3.144</v>
       </c>
       <c r="C18">
-        <v>0.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.512</v>
+        <v>14.578</v>
       </c>
       <c r="C19">
-        <v>1.162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>1.813</v>
+        <v>44.312</v>
       </c>
       <c r="C20">
-        <v>0.799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.089</v>
+        <v>17.418</v>
       </c>
       <c r="C21">
-        <v>0.95</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.082</v>
+        <v>7.777</v>
       </c>
       <c r="C22">
-        <v>13.109</v>
+        <v>1.766</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>2.264</v>
+        <v>1.093</v>
       </c>
       <c r="C23">
-        <v>0.089</v>
+        <v>11.844</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>4.878</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.659</v>
+        <v>16.203</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>12.757</v>
+        <v>0.788</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>3.852</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>0.881</v>
+        <v>3.467</v>
       </c>
       <c r="C26">
-        <v>7.377</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C27">
-        <v>9.622999999999999</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1.834</v>
       </c>
       <c r="C28">
-        <v>28.27</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>8.176</v>
       </c>
       <c r="C29">
-        <v>26.048</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="C30">
-        <v>4.891</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>4.206</v>
       </c>
       <c r="C31">
-        <v>6.584</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>3.962</v>
       </c>
       <c r="C32">
-        <v>4.244</v>
+        <v>2.214</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="C33">
-        <v>7.994</v>
+        <v>6.781</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>5.159</v>
       </c>
       <c r="C34">
+        <v>1.528</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>46133.34375</v>
+      </c>
+      <c r="B35">
+        <v>1.693</v>
+      </c>
+      <c r="C35">
+        <v>0.068</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>46133.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>12</v>
+      </c>
+      <c r="C36">
+        <v>0.191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>46133.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>3.555</v>
+      </c>
+      <c r="C37">
+        <v>1.371</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>46133.375</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>16.502</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>46133.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>9.989000000000001</v>
+      </c>
+      <c r="C39">
+        <v>1.606</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46133.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>2.635</v>
+      </c>
+      <c r="C40">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46133.40625</v>
+      </c>
+      <c r="B41">
+        <v>12.074</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46133.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>3.514</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46133.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,197 +400,197 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>28.43</v>
+        <v>65.876</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46139.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>41.326</v>
+        <v>77.233</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46139.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>32.276</v>
+        <v>33.688</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46139.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="C5">
-        <v>5.55</v>
+        <v>3.484</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46139.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2.487</v>
       </c>
       <c r="C6">
-        <v>51.713</v>
+        <v>2.826</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46139.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2.224</v>
       </c>
       <c r="C7">
-        <v>90.974</v>
+        <v>1.306</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46139.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>3.285</v>
       </c>
       <c r="C8">
-        <v>37.539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46139.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.232</v>
+        <v>1.275</v>
       </c>
       <c r="C9">
-        <v>3.134</v>
+        <v>1.171</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46139.08333333334</v>
       </c>
       <c r="B10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>5.875</v>
+        <v>20.474</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46139.09375</v>
       </c>
       <c r="B11">
-        <v>19.015</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>34.814</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46139.10416666666</v>
       </c>
       <c r="B12">
-        <v>6.204</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>4.984</v>
+        <v>16.089</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46139.11458333334</v>
       </c>
       <c r="B13">
-        <v>10.306</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46139.125</v>
       </c>
       <c r="B14">
-        <v>3.963</v>
+        <v>0.037</v>
       </c>
       <c r="C14">
-        <v>0.9370000000000001</v>
+        <v>13.239</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46139.13541666666</v>
       </c>
       <c r="B15">
-        <v>8.337999999999999</v>
+        <v>0.058</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>8.334</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46139.14583333334</v>
       </c>
       <c r="B16">
-        <v>11.435</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>48.235</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46139.15625</v>
       </c>
       <c r="B17">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>41.411</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46139.16666666666</v>
       </c>
       <c r="B18">
-        <v>3.144</v>
+        <v>4.179</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46139.17708333334</v>
       </c>
       <c r="B19">
-        <v>14.578</v>
+        <v>8.416</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,10 +598,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46139.1875</v>
       </c>
       <c r="B20">
-        <v>44.312</v>
+        <v>14.855</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,254 +609,375 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46139.19791666666</v>
       </c>
       <c r="B21">
-        <v>17.418</v>
+        <v>6.208</v>
       </c>
       <c r="C21">
-        <v>0.354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46139.20833333334</v>
       </c>
       <c r="B22">
-        <v>7.777</v>
+        <v>8.773</v>
       </c>
       <c r="C22">
-        <v>1.766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46139.21875</v>
       </c>
       <c r="B23">
-        <v>1.093</v>
+        <v>2.002</v>
       </c>
       <c r="C23">
-        <v>11.844</v>
+        <v>2.811</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46139.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1.464</v>
       </c>
       <c r="C24">
-        <v>16.203</v>
+        <v>1.309</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46139.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.788</v>
+        <v>3.834</v>
       </c>
       <c r="C25">
-        <v>3.852</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46139.25</v>
       </c>
       <c r="B26">
-        <v>3.467</v>
+        <v>0.093</v>
       </c>
       <c r="C26">
-        <v>0.07199999999999999</v>
+        <v>11.801</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46139.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>4.81</v>
+        <v>21.601</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46139.27083333334</v>
       </c>
       <c r="B28">
-        <v>1.834</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.91</v>
+        <v>7.271</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46139.28125</v>
       </c>
       <c r="B29">
-        <v>8.176</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.611</v>
+        <v>2.606</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46139.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.013</v>
+        <v>2.002</v>
       </c>
       <c r="C30">
-        <v>11.936</v>
+        <v>5.652</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46139.30208333334</v>
       </c>
       <c r="B31">
-        <v>4.206</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>3.045</v>
+        <v>3.901</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46139.3125</v>
       </c>
       <c r="B32">
-        <v>3.962</v>
+        <v>0.102</v>
       </c>
       <c r="C32">
-        <v>2.214</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46139.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>6.781</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46139.33333333334</v>
       </c>
       <c r="B34">
-        <v>5.159</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>1.528</v>
+        <v>11.629</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46139.34375</v>
       </c>
       <c r="B35">
-        <v>1.693</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.068</v>
+        <v>10.685</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46139.35416666666</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>0.04</v>
       </c>
       <c r="C36">
-        <v>0.191</v>
+        <v>2.169</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46139.36458333334</v>
       </c>
       <c r="B37">
-        <v>3.555</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>1.371</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46139.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>38.695</v>
       </c>
       <c r="C38">
-        <v>16.502</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46139.38541666666</v>
       </c>
       <c r="B39">
-        <v>9.989000000000001</v>
+        <v>24.76</v>
       </c>
       <c r="C39">
-        <v>1.606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46139.39583333334</v>
       </c>
       <c r="B40">
-        <v>2.635</v>
+        <v>6.059</v>
       </c>
       <c r="C40">
-        <v>0.11</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46139.40625</v>
       </c>
       <c r="B41">
-        <v>12.074</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1.744</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46139.41666666666</v>
       </c>
       <c r="B42">
-        <v>3.514</v>
+        <v>11.576</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46139.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>29.462</v>
       </c>
       <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46139.4375</v>
+      </c>
+      <c r="B44">
+        <v>13.518</v>
+      </c>
+      <c r="C44">
+        <v>0.079</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46139.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>8.938000000000001</v>
+      </c>
+      <c r="C45">
+        <v>0.514</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46139.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>8.493</v>
+      </c>
+      <c r="C46">
+        <v>0.196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46139.46875</v>
+      </c>
+      <c r="B47">
+        <v>58.894</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46139.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>24.803</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46139.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>6.767</v>
+      </c>
+      <c r="C49">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46139.5</v>
+      </c>
+      <c r="B50">
+        <v>1.048</v>
+      </c>
+      <c r="C50">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46139.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0.278</v>
+      </c>
+      <c r="C51">
+        <v>1.926</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46139.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0.003</v>
+      </c>
+      <c r="C52">
+        <v>2.824</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46139.53125</v>
+      </c>
+      <c r="B53">
+        <v>7.885</v>
+      </c>
+      <c r="C53">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46139.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,197 +400,197 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="C2">
-        <v>65.876</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46139.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="C3">
-        <v>77.233</v>
+        <v>16.238</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46139.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C4">
-        <v>33.688</v>
+        <v>7.805</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46139.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B5">
-        <v>0.158</v>
+        <v>3.337</v>
       </c>
       <c r="C5">
-        <v>3.484</v>
+        <v>1.074</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46139.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B6">
-        <v>2.487</v>
+        <v>3.571</v>
       </c>
       <c r="C6">
-        <v>2.826</v>
+        <v>4.499</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46139.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B7">
-        <v>2.224</v>
+        <v>0.268</v>
       </c>
       <c r="C7">
-        <v>1.306</v>
+        <v>6.028</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46139.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B8">
-        <v>3.285</v>
+        <v>1.687</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46139.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.275</v>
+        <v>1.144</v>
       </c>
       <c r="C9">
-        <v>1.171</v>
+        <v>5.155</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46139.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>7.039</v>
       </c>
       <c r="C10">
-        <v>20.474</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46139.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>8.619</v>
       </c>
       <c r="C11">
-        <v>34.814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46139.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2.963</v>
       </c>
       <c r="C12">
-        <v>16.089</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46139.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>18.35</v>
       </c>
       <c r="C13">
-        <v>13.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46139.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B14">
-        <v>0.037</v>
+        <v>31.715</v>
       </c>
       <c r="C14">
-        <v>13.239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46139.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.058</v>
+        <v>16.468</v>
       </c>
       <c r="C15">
-        <v>8.334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46139.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>33.675</v>
       </c>
       <c r="C16">
-        <v>48.235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46139.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>28.615</v>
       </c>
       <c r="C17">
-        <v>41.411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46139.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B18">
-        <v>4.179</v>
+        <v>24.273</v>
       </c>
       <c r="C18">
-        <v>2.848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46139.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B19">
-        <v>8.416</v>
+        <v>28.734</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,10 +598,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46139.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B20">
-        <v>14.855</v>
+        <v>17.16</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46139.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B21">
-        <v>6.208</v>
+        <v>5.357</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,285 +620,285 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46139.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B22">
-        <v>8.773</v>
+        <v>3.799</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3.094</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46139.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B23">
-        <v>2.002</v>
+        <v>3.513</v>
       </c>
       <c r="C23">
-        <v>2.811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46139.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.464</v>
+        <v>15.71</v>
       </c>
       <c r="C24">
-        <v>1.309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46139.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B25">
-        <v>3.834</v>
+        <v>17.483</v>
       </c>
       <c r="C25">
-        <v>2.664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46139.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B26">
-        <v>0.093</v>
+        <v>10.725</v>
       </c>
       <c r="C26">
-        <v>11.801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46139.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>4.116</v>
       </c>
       <c r="C27">
-        <v>21.601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46139.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1.723</v>
       </c>
       <c r="C28">
-        <v>7.271</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46139.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>5.633</v>
       </c>
       <c r="C29">
-        <v>2.606</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46139.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B30">
-        <v>2.002</v>
+        <v>10.802</v>
       </c>
       <c r="C30">
-        <v>5.652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46139.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>9.109</v>
       </c>
       <c r="C31">
-        <v>3.901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46139.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B32">
-        <v>0.102</v>
+        <v>4.295</v>
       </c>
       <c r="C32">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46139.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2.102</v>
       </c>
       <c r="C33">
-        <v>5.53</v>
+        <v>2.904</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46139.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="C34">
-        <v>11.629</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46139.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="C35">
-        <v>10.685</v>
+        <v>8.826000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46139.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>2.169</v>
+        <v>29.675</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46139.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0.838</v>
+        <v>30.537</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46139.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B38">
-        <v>38.695</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.04</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46139.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B39">
-        <v>24.76</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>13.776</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46139.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B40">
-        <v>6.059</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.908</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46139.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>1.744</v>
+        <v>2.039</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46139.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B42">
-        <v>11.576</v>
+        <v>1.801</v>
       </c>
       <c r="C42">
-        <v>0.239</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46139.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B43">
-        <v>29.462</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>6.886</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46139.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B44">
-        <v>13.518</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0.079</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46139.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B45">
-        <v>8.938000000000001</v>
+        <v>2.599</v>
       </c>
       <c r="C45">
-        <v>0.514</v>
+        <v>2.035</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46139.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B46">
-        <v>8.493</v>
+        <v>14.383</v>
       </c>
       <c r="C46">
-        <v>0.196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46139.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B47">
-        <v>58.894</v>
+        <v>8.631</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46139.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B48">
-        <v>24.803</v>
+        <v>4.499</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -917,67 +917,12 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>46139.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B49">
-        <v>6.767</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0.033</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46139.5</v>
-      </c>
-      <c r="B50">
-        <v>1.048</v>
-      </c>
-      <c r="C50">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46139.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0.278</v>
-      </c>
-      <c r="C51">
-        <v>1.926</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46139.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0.003</v>
-      </c>
-      <c r="C52">
-        <v>2.824</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46139.53125</v>
-      </c>
-      <c r="B53">
-        <v>7.885</v>
-      </c>
-      <c r="C53">
-        <v>0.172</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46139.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,131 +400,131 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B2">
-        <v>0.076</v>
+        <v>2.385</v>
       </c>
       <c r="C2">
-        <v>10.166</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46142.01041666666</v>
+        <v>46146.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.102</v>
+        <v>0.992</v>
       </c>
       <c r="C3">
-        <v>16.238</v>
+        <v>1.882</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46142.02083333334</v>
+        <v>46146.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>7.805</v>
+        <v>14.561</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46142.03125</v>
+        <v>46146.03125</v>
       </c>
       <c r="B5">
-        <v>3.337</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1.074</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46142.04166666666</v>
+        <v>46146.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.571</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>4.499</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46142.05208333334</v>
+        <v>46146.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.268</v>
+        <v>0.123</v>
       </c>
       <c r="C7">
-        <v>6.028</v>
+        <v>1.114</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46142.0625</v>
+        <v>46146.0625</v>
       </c>
       <c r="B8">
-        <v>1.687</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2.655</v>
+        <v>18.359</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46142.07291666666</v>
+        <v>46146.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.144</v>
+        <v>0.774</v>
       </c>
       <c r="C9">
-        <v>5.155</v>
+        <v>6.549</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46142.08333333334</v>
+        <v>46146.08333333334</v>
       </c>
       <c r="B10">
-        <v>7.039</v>
+        <v>0.649</v>
       </c>
       <c r="C10">
-        <v>0.988</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46142.09375</v>
+        <v>46146.09375</v>
       </c>
       <c r="B11">
-        <v>8.619</v>
+        <v>4.818</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2.232</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46142.10416666666</v>
+        <v>46146.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.963</v>
+        <v>4.879</v>
       </c>
       <c r="C12">
-        <v>0.067</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46142.11458333334</v>
+        <v>46146.11458333334</v>
       </c>
       <c r="B13">
-        <v>18.35</v>
+        <v>16.524</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -532,10 +532,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46142.125</v>
+        <v>46146.125</v>
       </c>
       <c r="B14">
-        <v>31.715</v>
+        <v>11.286</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -543,386 +543,265 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46142.13541666666</v>
+        <v>46146.13541666666</v>
       </c>
       <c r="B15">
-        <v>16.468</v>
+        <v>4.8</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46142.14583333334</v>
+        <v>46146.14583333334</v>
       </c>
       <c r="B16">
-        <v>33.675</v>
+        <v>2.231</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46142.15625</v>
+        <v>46146.15625</v>
       </c>
       <c r="B17">
-        <v>28.615</v>
+        <v>2.029</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46142.16666666666</v>
+        <v>46146.16666666666</v>
       </c>
       <c r="B18">
-        <v>24.273</v>
+        <v>0.152</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>8.763</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46142.17708333334</v>
+        <v>46146.17708333334</v>
       </c>
       <c r="B19">
-        <v>28.734</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>27.058</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46142.1875</v>
+        <v>46146.1875</v>
       </c>
       <c r="B20">
-        <v>17.16</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>48.787</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46142.19791666666</v>
+        <v>46146.19791666666</v>
       </c>
       <c r="B21">
-        <v>5.357</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>42.735</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46142.20833333334</v>
+        <v>46146.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.799</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>3.094</v>
+        <v>49.211</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46142.21875</v>
+        <v>46146.21875</v>
       </c>
       <c r="B23">
-        <v>3.513</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>51.124</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46142.22916666666</v>
+        <v>46146.22916666666</v>
       </c>
       <c r="B24">
-        <v>15.71</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>16.887</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46142.23958333334</v>
+        <v>46146.23958333334</v>
       </c>
       <c r="B25">
-        <v>17.483</v>
+        <v>0.783</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46142.25</v>
+        <v>46146.25</v>
       </c>
       <c r="B26">
-        <v>10.725</v>
+        <v>0.043</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>7.813</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46142.26041666666</v>
+        <v>46146.26041666666</v>
       </c>
       <c r="B27">
-        <v>4.116</v>
+        <v>0.09</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>9.571</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46142.27083333334</v>
+        <v>46146.27083333334</v>
       </c>
       <c r="B28">
-        <v>1.723</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.068</v>
+        <v>15.893</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46142.28125</v>
+        <v>46146.28125</v>
       </c>
       <c r="B29">
-        <v>5.633</v>
+        <v>0.015</v>
       </c>
       <c r="C29">
-        <v>0.977</v>
+        <v>12.152</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46142.29166666666</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="B30">
-        <v>10.802</v>
+        <v>0.034</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>20.255</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46142.30208333334</v>
+        <v>46146.30208333334</v>
       </c>
       <c r="B31">
-        <v>9.109</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>40.971</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46142.3125</v>
+        <v>46146.3125</v>
       </c>
       <c r="B32">
-        <v>4.295</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>8.007999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46142.32291666666</v>
+        <v>46146.32291666666</v>
       </c>
       <c r="B33">
-        <v>2.102</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>2.904</v>
+        <v>1.408</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46142.33333333334</v>
+        <v>46146.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.223</v>
+        <v>4.21</v>
       </c>
       <c r="C34">
-        <v>12.31</v>
+        <v>1.027</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46142.34375</v>
+        <v>46146.34375</v>
       </c>
       <c r="B35">
-        <v>0.121</v>
+        <v>10.321</v>
       </c>
       <c r="C35">
-        <v>8.826000000000001</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46142.35416666666</v>
+        <v>46146.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>29.675</v>
+        <v>4.148</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46142.36458333334</v>
+        <v>46146.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="C37">
-        <v>30.537</v>
+        <v>3.428</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46142.375</v>
+        <v>46146.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>16.08</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46142.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
-        <v>13.776</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46142.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>9.32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46142.40625</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>2.039</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46142.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>1.801</v>
-      </c>
-      <c r="C42">
-        <v>3.609</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46142.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>6.886</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46142.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>14.16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46142.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>2.599</v>
-      </c>
-      <c r="C45">
-        <v>2.035</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46142.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>14.383</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46142.46875</v>
-      </c>
-      <c r="B47">
-        <v>8.631</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46142.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>4.499</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46142.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,408 +400,353 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B2">
-        <v>2.385</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.53</v>
+        <v>21.695</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46146.01041666666</v>
+        <v>46148.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.992</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1.882</v>
+        <v>30.861</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46146.02083333334</v>
+        <v>46148.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>14.561</v>
+        <v>26.636</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46146.03125</v>
+        <v>46148.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>23.07</v>
+        <v>25.163</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46146.04166666666</v>
+        <v>46148.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>15.01</v>
+        <v>68.864</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46146.05208333334</v>
+        <v>46148.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1.114</v>
+        <v>19.681</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46146.0625</v>
+        <v>46148.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="C8">
-        <v>18.359</v>
+        <v>4.275</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46146.07291666666</v>
+        <v>46148.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.774</v>
+        <v>0.993</v>
       </c>
       <c r="C9">
-        <v>6.549</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46146.08333333334</v>
+        <v>46148.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.649</v>
+        <v>0.791</v>
       </c>
       <c r="C10">
-        <v>2.93</v>
+        <v>1.993</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46146.09375</v>
+        <v>46148.09375</v>
       </c>
       <c r="B11">
-        <v>4.818</v>
+        <v>0.026</v>
       </c>
       <c r="C11">
-        <v>2.232</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46146.10416666666</v>
+        <v>46148.10416666666</v>
       </c>
       <c r="B12">
-        <v>4.879</v>
+        <v>2.285</v>
       </c>
       <c r="C12">
-        <v>0.635</v>
+        <v>1.769</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46146.11458333334</v>
+        <v>46148.11458333334</v>
       </c>
       <c r="B13">
-        <v>16.524</v>
+        <v>0.326</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>12.046</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46146.125</v>
+        <v>46148.125</v>
       </c>
       <c r="B14">
-        <v>11.286</v>
+        <v>0.867</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46146.13541666666</v>
+        <v>46148.13541666666</v>
       </c>
       <c r="B15">
-        <v>4.8</v>
+        <v>0.36</v>
       </c>
       <c r="C15">
-        <v>0.08699999999999999</v>
+        <v>4.143</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46146.14583333334</v>
+        <v>46148.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.231</v>
+        <v>4.229</v>
       </c>
       <c r="C16">
-        <v>0.309</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46146.15625</v>
+        <v>46148.15625</v>
       </c>
       <c r="B17">
-        <v>2.029</v>
+        <v>1.92</v>
       </c>
       <c r="C17">
-        <v>1.415</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46146.16666666666</v>
+        <v>46148.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>8.763</v>
+        <v>19.412</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46146.17708333334</v>
+        <v>46148.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C19">
-        <v>27.058</v>
+        <v>10.091</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46146.1875</v>
+        <v>46148.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>48.787</v>
+        <v>11.748</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46146.19791666666</v>
+        <v>46148.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>42.735</v>
+        <v>12.461</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46146.20833333334</v>
+        <v>46148.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>0.505</v>
       </c>
       <c r="C22">
-        <v>49.211</v>
+        <v>14.794</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46146.21875</v>
+        <v>46148.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>51.124</v>
+        <v>34.716</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46146.22916666666</v>
+        <v>46148.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>16.887</v>
+        <v>12.114</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46146.23958333334</v>
+        <v>46148.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.783</v>
+        <v>0.122</v>
       </c>
       <c r="C25">
-        <v>6.86</v>
+        <v>8.673999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46146.25</v>
+        <v>46148.25</v>
       </c>
       <c r="B26">
-        <v>0.043</v>
+        <v>0.011</v>
       </c>
       <c r="C26">
-        <v>7.813</v>
+        <v>28.176</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46146.26041666666</v>
+        <v>46148.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>9.571</v>
+        <v>31.491</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46146.27083333334</v>
+        <v>46148.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>15.893</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46146.28125</v>
+        <v>46148.28125</v>
       </c>
       <c r="B29">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>12.152</v>
+        <v>25.689</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46146.29166666666</v>
+        <v>46148.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.034</v>
+        <v>4.772</v>
       </c>
       <c r="C30">
-        <v>20.255</v>
+        <v>8.643000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46146.30208333334</v>
+        <v>46148.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="C31">
-        <v>40.971</v>
+        <v>5.643</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46146.3125</v>
+        <v>46148.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>3.803</v>
       </c>
       <c r="C32">
-        <v>8.007999999999999</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46146.32291666666</v>
+        <v>46148.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1.408</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2">
-        <v>46146.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>4.21</v>
-      </c>
-      <c r="C34">
-        <v>1.027</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
-        <v>46146.34375</v>
-      </c>
-      <c r="B35">
-        <v>10.321</v>
-      </c>
-      <c r="C35">
-        <v>0.077</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
-        <v>46146.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>4.148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
-        <v>46146.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="C37">
-        <v>3.428</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46146.375</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,353 +400,386 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>21.695</v>
+        <v>25.907</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>30.861</v>
+        <v>37.492</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>26.636</v>
+        <v>61.003</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>25.163</v>
+        <v>14.342</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>68.864</v>
+        <v>12.729</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>19.681</v>
+        <v>4.737</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B8">
-        <v>0.743</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>4.275</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.993</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>4.36</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.791</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1.993</v>
+        <v>44.817</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B11">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>8.619999999999999</v>
+        <v>28.638</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.285</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1.769</v>
+        <v>27.749</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.326</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>12.046</v>
+        <v>7.009</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B14">
-        <v>0.867</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>2.754</v>
+        <v>17.961</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="C15">
-        <v>4.143</v>
+        <v>1.676</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B16">
-        <v>4.229</v>
+        <v>0.98</v>
       </c>
       <c r="C16">
-        <v>0.658</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B17">
-        <v>1.92</v>
+        <v>0.137</v>
       </c>
       <c r="C17">
-        <v>1.83</v>
+        <v>8.271000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>19.412</v>
+        <v>50.031</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>10.091</v>
+        <v>44.218</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>11.748</v>
+        <v>31.347</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>12.461</v>
+        <v>49.567</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.505</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>14.794</v>
+        <v>74.217</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>34.716</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>12.114</v>
+        <v>30.356</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>8.673999999999999</v>
+        <v>22.194</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B26">
-        <v>0.011</v>
+        <v>0.043</v>
       </c>
       <c r="C26">
-        <v>28.176</v>
+        <v>17.756</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>31.491</v>
+        <v>40.614</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>22.22</v>
+        <v>23.963</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C29">
-        <v>25.689</v>
+        <v>10.752</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B30">
-        <v>4.772</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>8.643000000000001</v>
+        <v>20.995</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>5.643</v>
+        <v>37.877</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B32">
-        <v>3.803</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.293</v>
+        <v>23.161</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
+        <v>45.686</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2">
+        <v>46150.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>47.611</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>46150.34375</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>26.121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>46150.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,386 +400,485 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2.166</v>
       </c>
       <c r="C2">
-        <v>25.907</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="C3">
-        <v>37.492</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C4">
-        <v>61.003</v>
+        <v>6.883</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5.171</v>
       </c>
       <c r="C5">
-        <v>14.342</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C6">
-        <v>12.729</v>
+        <v>16.399</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>4.737</v>
+        <v>21.468</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>14.93</v>
+        <v>31.148</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>21.7</v>
+        <v>10.596</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>44.817</v>
+        <v>34.108</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="C11">
-        <v>28.638</v>
+        <v>12.505</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>4.539</v>
       </c>
       <c r="C12">
-        <v>27.749</v>
+        <v>2.219</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="C13">
-        <v>7.009</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>16.023</v>
       </c>
       <c r="C14">
-        <v>17.961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.4</v>
+        <v>43.065</v>
       </c>
       <c r="C15">
-        <v>1.676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.98</v>
+        <v>34.676</v>
       </c>
       <c r="C16">
-        <v>8.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B17">
-        <v>0.137</v>
+        <v>41.049</v>
       </c>
       <c r="C17">
-        <v>8.271000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>36.891</v>
       </c>
       <c r="C18">
-        <v>50.031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>37.504</v>
       </c>
       <c r="C19">
-        <v>44.218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>23.896</v>
       </c>
       <c r="C20">
-        <v>31.347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>10.418</v>
       </c>
       <c r="C21">
-        <v>49.567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2.227</v>
       </c>
       <c r="C22">
-        <v>74.217</v>
+        <v>7.999</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>11.232</v>
       </c>
       <c r="C23">
-        <v>42.26</v>
+        <v>3.282</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>5.018</v>
       </c>
       <c r="C24">
-        <v>30.356</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>8.657999999999999</v>
       </c>
       <c r="C25">
-        <v>22.194</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B26">
-        <v>0.043</v>
+        <v>5.897</v>
       </c>
       <c r="C26">
-        <v>17.756</v>
+        <v>2.146</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>28.204</v>
       </c>
       <c r="C27">
-        <v>40.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>4.809</v>
       </c>
       <c r="C28">
-        <v>23.963</v>
+        <v>2.812</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B29">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="C29">
-        <v>10.752</v>
+        <v>6.594</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>20.995</v>
+        <v>36.781</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>37.877</v>
+        <v>22.224</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>23.161</v>
+        <v>38.009</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>10.203</v>
       </c>
       <c r="C33">
-        <v>45.686</v>
+        <v>1.944</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>101.061</v>
       </c>
       <c r="C34">
-        <v>47.611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>84.824</v>
       </c>
       <c r="C35">
-        <v>26.121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>52.212</v>
       </c>
       <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>46154.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>65.379</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>46154.375</v>
+      </c>
+      <c r="B38">
+        <v>82.655</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>46154.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>51.808</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46154.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>0.63</v>
+      </c>
+      <c r="C40">
+        <v>7.149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46154.40625</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>17.854</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46154.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>98.19499999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46154.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>18.347</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46154.4375</v>
+      </c>
+      <c r="B44">
+        <v>6.683</v>
+      </c>
+      <c r="C44">
+        <v>4.389</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46154.45833333334</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,485 +400,595 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>2.166</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.632</v>
+        <v>3.046</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46154.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.222</v>
+        <v>0.989</v>
       </c>
       <c r="C3">
-        <v>1.896</v>
+        <v>5.585</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46154.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.017</v>
+        <v>3.227</v>
       </c>
       <c r="C4">
-        <v>6.883</v>
+        <v>3.374</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46154.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>5.171</v>
+        <v>9.474</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46154.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.08</v>
+        <v>11.641</v>
       </c>
       <c r="C6">
-        <v>16.399</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46154.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>27.14</v>
       </c>
       <c r="C7">
-        <v>21.468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46154.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>21.925</v>
       </c>
       <c r="C8">
-        <v>31.148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46154.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>20.092</v>
       </c>
       <c r="C9">
-        <v>10.596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46154.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>11.556</v>
       </c>
       <c r="C10">
-        <v>34.108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46154.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>0.497</v>
+        <v>8.425000000000001</v>
       </c>
       <c r="C11">
-        <v>12.505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46154.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>4.539</v>
+        <v>9.231</v>
       </c>
       <c r="C12">
-        <v>2.219</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46154.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>4.63</v>
+        <v>5.516</v>
       </c>
       <c r="C13">
-        <v>0.89</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46154.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>16.023</v>
+        <v>0.442</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1.389</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46154.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>43.065</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46154.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>34.676</v>
+        <v>0.013</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>5.294</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46154.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>41.049</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46154.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>36.891</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1.911</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46154.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>37.504</v>
+        <v>0.004</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46154.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>23.896</v>
+        <v>3.536</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46154.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>10.418</v>
+        <v>0.29</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46154.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.227</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>7.999</v>
+        <v>21.309</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46154.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>11.232</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>3.282</v>
+        <v>24.433</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46154.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>5.018</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.741</v>
+        <v>21.927</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46154.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>8.657999999999999</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1.13</v>
+        <v>28.357</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46154.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>5.897</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>2.146</v>
+        <v>18.468</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46154.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>28.204</v>
+        <v>0.074</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>9.989000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46154.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>4.809</v>
+        <v>0.544</v>
       </c>
       <c r="C28">
-        <v>2.812</v>
+        <v>4.945</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46154.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>0.001</v>
+        <v>2.39</v>
       </c>
       <c r="C29">
-        <v>6.594</v>
+        <v>3.377</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46154.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>3.359</v>
       </c>
       <c r="C30">
-        <v>36.781</v>
+        <v>1.383</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46154.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="C31">
-        <v>22.224</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46154.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1.303</v>
       </c>
       <c r="C32">
-        <v>38.009</v>
+        <v>9.819000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46154.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>10.203</v>
+        <v>0.19</v>
       </c>
       <c r="C33">
-        <v>1.944</v>
+        <v>19.862</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46154.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>101.061</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>39.092</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46154.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>84.824</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>34.537</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46154.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>52.212</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46154.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>65.379</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>12.529</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46154.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>82.655</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>26.745</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46154.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>51.808</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>14.862</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46154.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>7.149</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46154.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2.261</v>
       </c>
       <c r="C41">
-        <v>17.854</v>
+        <v>2.643</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46154.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>17.894</v>
       </c>
       <c r="C42">
-        <v>98.19499999999999</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46154.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>36.323</v>
       </c>
       <c r="C43">
-        <v>18.347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46154.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>6.683</v>
+        <v>24.688</v>
       </c>
       <c r="C44">
-        <v>4.389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46154.45833333334</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>7.913</v>
       </c>
       <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46155.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>39.893</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46155.46875</v>
+      </c>
+      <c r="B47">
+        <v>4.946</v>
+      </c>
+      <c r="C47">
+        <v>2.109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46155.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>7.711</v>
+      </c>
+      <c r="C48">
+        <v>0.524</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46155.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>0.015</v>
+      </c>
+      <c r="C49">
+        <v>6.201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46155.5</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>14.97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46155.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>12.752</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46155.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>9.625</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46155.53125</v>
+      </c>
+      <c r="B53">
+        <v>1.785</v>
+      </c>
+      <c r="C53">
+        <v>2.219</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46155.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2">
+        <v>46155.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,595 +400,584 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.046</v>
+        <v>11.469</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.989</v>
+        <v>1.31</v>
       </c>
       <c r="C3">
-        <v>5.585</v>
+        <v>2.159</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
-        <v>3.227</v>
+        <v>0.675</v>
       </c>
       <c r="C4">
-        <v>3.374</v>
+        <v>4.184</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
-        <v>9.474</v>
+        <v>0.035</v>
       </c>
       <c r="C5">
-        <v>0.006</v>
+        <v>6.624</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>11.641</v>
+        <v>3.27</v>
       </c>
       <c r="C6">
-        <v>0.124</v>
+        <v>2.494</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>27.14</v>
+        <v>0.637</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2.799</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>21.925</v>
+        <v>0.217</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>20.092</v>
+        <v>0.018</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>9.031000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>11.556</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>32.234</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>8.425000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>3.578</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>9.231</v>
+        <v>0.064</v>
       </c>
       <c r="C12">
-        <v>0.034</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>5.516</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.004</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>0.442</v>
+        <v>0.008</v>
       </c>
       <c r="C14">
-        <v>1.389</v>
+        <v>13.404</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>1.175</v>
+        <v>1.866</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="C16">
-        <v>5.294</v>
+        <v>2.239</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>7.5</v>
+        <v>8.064</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>1.911</v>
+        <v>22.555</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.004</v>
+        <v>0.025</v>
       </c>
       <c r="C19">
-        <v>3.44</v>
+        <v>4.785</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>3.536</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1.416</v>
+        <v>14.609</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.29</v>
+        <v>0.083</v>
       </c>
       <c r="C21">
-        <v>12.43</v>
+        <v>16.424</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C22">
-        <v>21.309</v>
+        <v>20.977</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C23">
-        <v>24.433</v>
+        <v>9.391999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>6.824</v>
       </c>
       <c r="C24">
-        <v>21.927</v>
+        <v>1.413</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>14.957</v>
       </c>
       <c r="C25">
-        <v>28.357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>7.947</v>
       </c>
       <c r="C26">
-        <v>18.468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.074</v>
+        <v>0.523</v>
       </c>
       <c r="C27">
-        <v>9.989000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.544</v>
+        <v>4.481</v>
       </c>
       <c r="C28">
-        <v>4.945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>2.39</v>
+        <v>7.987</v>
       </c>
       <c r="C29">
-        <v>3.377</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>3.359</v>
+        <v>0.312</v>
       </c>
       <c r="C30">
-        <v>1.383</v>
+        <v>9.845000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>1.975</v>
+        <v>23.029</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>1.303</v>
+        <v>4.486</v>
       </c>
       <c r="C32">
-        <v>9.819000000000001</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.19</v>
+        <v>3.917</v>
       </c>
       <c r="C33">
-        <v>19.862</v>
+        <v>2.159</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="C34">
-        <v>39.092</v>
+        <v>22.278</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2.788</v>
       </c>
       <c r="C35">
-        <v>34.537</v>
+        <v>3.337</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>5.411</v>
       </c>
       <c r="C36">
-        <v>24.42</v>
+        <v>4.006</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>42.968</v>
       </c>
       <c r="C37">
-        <v>12.529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>26.873</v>
       </c>
       <c r="C38">
-        <v>26.745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>28.946</v>
       </c>
       <c r="C39">
-        <v>14.862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>15.753</v>
       </c>
       <c r="C40">
-        <v>9.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>2.261</v>
+        <v>28.22</v>
       </c>
       <c r="C41">
-        <v>2.643</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>17.894</v>
+        <v>26.228</v>
       </c>
       <c r="C42">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>36.323</v>
+        <v>6.599</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1.353</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>24.688</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>6.664</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>7.913</v>
+        <v>13.073</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>3.729</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>39.893</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>17.209</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>4.946</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>2.109</v>
+        <v>12.761</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>7.711</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C48">
-        <v>0.524</v>
+        <v>16.075</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.015</v>
+        <v>0.624</v>
       </c>
       <c r="C49">
-        <v>6.201</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>14.97</v>
+        <v>11.748</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="C51">
-        <v>12.752</v>
+        <v>16.742</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>3.961</v>
       </c>
       <c r="C52">
-        <v>9.625</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>1.785</v>
+        <v>13.482</v>
       </c>
       <c r="C53">
-        <v>2.219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
-        <v>46155.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,285 +400,285 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.924</v>
       </c>
       <c r="C2">
-        <v>11.469</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.31</v>
+        <v>3.575</v>
       </c>
       <c r="C3">
-        <v>2.159</v>
+        <v>1.031</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.675</v>
+        <v>5.903</v>
       </c>
       <c r="C4">
-        <v>4.184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
-        <v>0.035</v>
+        <v>2.234</v>
       </c>
       <c r="C5">
-        <v>6.624</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.27</v>
+        <v>0.839</v>
       </c>
       <c r="C6">
-        <v>2.494</v>
+        <v>3.071</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.637</v>
+        <v>4.131</v>
       </c>
       <c r="C7">
-        <v>2.799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>0.217</v>
+        <v>0.445</v>
       </c>
       <c r="C8">
-        <v>2.835</v>
+        <v>2.297</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>9.031000000000001</v>
+        <v>7.735</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>32.234</v>
+        <v>16.052</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>0.232</v>
+        <v>0.073</v>
       </c>
       <c r="C11">
-        <v>3.578</v>
+        <v>11.148</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.064</v>
+        <v>0.172</v>
       </c>
       <c r="C12">
-        <v>0.996</v>
+        <v>4.556</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>3.108</v>
       </c>
       <c r="C13">
-        <v>0.647</v>
+        <v>1.122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>13.404</v>
+        <v>6.939</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.259</v>
       </c>
       <c r="C15">
-        <v>1.866</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.001</v>
+        <v>2.66</v>
       </c>
       <c r="C16">
-        <v>2.239</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>5.489</v>
       </c>
       <c r="C17">
-        <v>8.064</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="C18">
-        <v>22.555</v>
+        <v>2.212</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.025</v>
+        <v>0.766</v>
       </c>
       <c r="C19">
-        <v>4.785</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>4.193</v>
       </c>
       <c r="C20">
-        <v>14.609</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.083</v>
+        <v>3.202</v>
       </c>
       <c r="C21">
-        <v>16.424</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.01</v>
+        <v>2.261</v>
       </c>
       <c r="C22">
-        <v>20.977</v>
+        <v>3.966</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>0.002</v>
+        <v>1.174</v>
       </c>
       <c r="C23">
-        <v>9.391999999999999</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>6.824</v>
+        <v>11.976</v>
       </c>
       <c r="C24">
-        <v>1.413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>14.957</v>
+        <v>17.021</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>7.947</v>
+        <v>0.78</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.523</v>
+        <v>8.618</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -686,10 +686,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>4.481</v>
+        <v>5.603</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -697,109 +697,109 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>7.987</v>
+        <v>12.469</v>
       </c>
       <c r="C29">
-        <v>0.647</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.312</v>
+        <v>13.8</v>
       </c>
       <c r="C30">
-        <v>9.845000000000001</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>31.325</v>
       </c>
       <c r="C31">
-        <v>23.029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>4.486</v>
+        <v>42.574</v>
       </c>
       <c r="C32">
-        <v>0.699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>3.917</v>
+        <v>7.491</v>
       </c>
       <c r="C33">
-        <v>2.159</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.023</v>
+        <v>1.186</v>
       </c>
       <c r="C34">
-        <v>22.278</v>
+        <v>3.437</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>2.788</v>
+        <v>2.211</v>
       </c>
       <c r="C35">
-        <v>3.337</v>
+        <v>6.717</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>5.411</v>
+        <v>29.07</v>
       </c>
       <c r="C36">
-        <v>4.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>42.968</v>
+        <v>15.053</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>26.873</v>
+        <v>23.588</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -807,177 +807,166 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>28.946</v>
+        <v>0.491</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>17.424</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>15.753</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>22.062</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>28.22</v>
+        <v>0.648</v>
       </c>
       <c r="C41">
-        <v>0.08799999999999999</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>26.228</v>
+        <v>5.105</v>
       </c>
       <c r="C42">
-        <v>0.006</v>
+        <v>1.287</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>6.599</v>
+        <v>1.296</v>
       </c>
       <c r="C43">
-        <v>1.353</v>
+        <v>3.595</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>22.112</v>
       </c>
       <c r="C44">
-        <v>6.664</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>13.073</v>
+        <v>12.928</v>
       </c>
       <c r="C45">
-        <v>3.729</v>
+        <v>4.603</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1.916</v>
       </c>
       <c r="C46">
-        <v>17.209</v>
+        <v>5.803</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>0.732</v>
       </c>
       <c r="C47">
-        <v>12.761</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>16.075</v>
+        <v>4.275</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.624</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>7.344</v>
+        <v>1.491</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="C50">
-        <v>11.748</v>
+        <v>1.914</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.256</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>16.742</v>
+        <v>5.099</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>3.961</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0.063</v>
+        <v>16.996</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>13.482</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46163.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,32 +400,32 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B2">
-        <v>0.924</v>
+        <v>17.803</v>
       </c>
       <c r="C2">
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46164.01041666666</v>
+        <v>46167.01041666666</v>
       </c>
       <c r="B3">
-        <v>3.575</v>
+        <v>10.605</v>
       </c>
       <c r="C3">
-        <v>1.031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46164.02083333334</v>
+        <v>46167.02083333334</v>
       </c>
       <c r="B4">
-        <v>5.903</v>
+        <v>8.381</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -433,32 +433,32 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46164.03125</v>
+        <v>46167.03125</v>
       </c>
       <c r="B5">
-        <v>2.234</v>
+        <v>14.65</v>
       </c>
       <c r="C5">
-        <v>0.978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46164.04166666666</v>
+        <v>46167.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.839</v>
+        <v>4.432</v>
       </c>
       <c r="C6">
-        <v>3.071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46164.05208333334</v>
+        <v>46167.05208333334</v>
       </c>
       <c r="B7">
-        <v>4.131</v>
+        <v>2.368</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -466,507 +466,430 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46164.0625</v>
+        <v>46167.0625</v>
       </c>
       <c r="B8">
-        <v>0.445</v>
+        <v>2.524</v>
       </c>
       <c r="C8">
-        <v>2.297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46164.07291666666</v>
+        <v>46167.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>3.283</v>
       </c>
       <c r="C9">
-        <v>7.735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46164.08333333334</v>
+        <v>46167.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>3.366</v>
       </c>
       <c r="C10">
-        <v>16.052</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46164.09375</v>
+        <v>46167.09375</v>
       </c>
       <c r="B11">
-        <v>0.073</v>
+        <v>0.057</v>
       </c>
       <c r="C11">
-        <v>11.148</v>
+        <v>4.653</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46164.10416666666</v>
+        <v>46167.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>4.556</v>
+        <v>24.672</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46164.11458333334</v>
+        <v>46167.11458333334</v>
       </c>
       <c r="B13">
-        <v>3.108</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1.122</v>
+        <v>48.995</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46164.125</v>
+        <v>46167.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>6.939</v>
+        <v>61.361</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46164.13541666666</v>
+        <v>46167.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>4.08</v>
+        <v>35.966</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46164.14583333334</v>
+        <v>46167.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0.659</v>
+        <v>9.002000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46164.15625</v>
+        <v>46167.15625</v>
       </c>
       <c r="B17">
-        <v>5.489</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.089</v>
+        <v>9.913</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46164.16666666666</v>
+        <v>46167.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.14</v>
+        <v>5.433</v>
       </c>
       <c r="C18">
-        <v>2.212</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46164.17708333334</v>
+        <v>46167.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.766</v>
+        <v>12.526</v>
       </c>
       <c r="C19">
-        <v>0.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46164.1875</v>
+        <v>46167.1875</v>
       </c>
       <c r="B20">
-        <v>4.193</v>
+        <v>16.311</v>
       </c>
       <c r="C20">
-        <v>0.245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46164.19791666666</v>
+        <v>46167.19791666666</v>
       </c>
       <c r="B21">
-        <v>3.202</v>
+        <v>5.014</v>
       </c>
       <c r="C21">
-        <v>0.021</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46164.20833333334</v>
+        <v>46167.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.261</v>
+        <v>0.384</v>
       </c>
       <c r="C22">
-        <v>3.966</v>
+        <v>23.104</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46164.21875</v>
+        <v>46167.21875</v>
       </c>
       <c r="B23">
-        <v>1.174</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0.828</v>
+        <v>22.383</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46164.22916666666</v>
+        <v>46167.22916666666</v>
       </c>
       <c r="B24">
-        <v>11.976</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46164.23958333334</v>
+        <v>46167.23958333334</v>
       </c>
       <c r="B25">
-        <v>17.021</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.647</v>
+        <v>24.209</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46164.25</v>
+        <v>46167.25</v>
       </c>
       <c r="B26">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.888</v>
+        <v>47.808</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46164.26041666666</v>
+        <v>46167.26041666666</v>
       </c>
       <c r="B27">
-        <v>8.618</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>55.483</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46164.27083333334</v>
+        <v>46167.27083333334</v>
       </c>
       <c r="B28">
-        <v>5.603</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>29.503</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46164.28125</v>
+        <v>46167.28125</v>
       </c>
       <c r="B29">
-        <v>12.469</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.08500000000000001</v>
+        <v>13.124</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46164.29166666666</v>
+        <v>46167.29166666666</v>
       </c>
       <c r="B30">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.004</v>
+        <v>35.495</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46164.30208333334</v>
+        <v>46167.30208333334</v>
       </c>
       <c r="B31">
-        <v>31.325</v>
+        <v>0.334</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>5.635</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46164.3125</v>
+        <v>46167.3125</v>
       </c>
       <c r="B32">
-        <v>42.574</v>
+        <v>6.287</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46164.32291666666</v>
+        <v>46167.32291666666</v>
       </c>
       <c r="B33">
-        <v>7.491</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.802</v>
+        <v>7.265</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46164.33333333334</v>
+        <v>46167.33333333334</v>
       </c>
       <c r="B34">
-        <v>1.186</v>
+        <v>8.984</v>
       </c>
       <c r="C34">
-        <v>3.437</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46164.34375</v>
+        <v>46167.34375</v>
       </c>
       <c r="B35">
-        <v>2.211</v>
+        <v>5.44</v>
       </c>
       <c r="C35">
-        <v>6.717</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46164.35416666666</v>
+        <v>46167.35416666666</v>
       </c>
       <c r="B36">
-        <v>29.07</v>
+        <v>0.363</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1.124</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46164.36458333334</v>
+        <v>46167.36458333334</v>
       </c>
       <c r="B37">
-        <v>15.053</v>
+        <v>2.702</v>
       </c>
       <c r="C37">
-        <v>0.013</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46164.375</v>
+        <v>46167.375</v>
       </c>
       <c r="B38">
-        <v>23.588</v>
+        <v>7.082</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46164.38541666666</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.491</v>
+        <v>0.024</v>
       </c>
       <c r="C39">
-        <v>17.424</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46164.39583333334</v>
+        <v>46167.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>22.062</v>
+        <v>28.867</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46164.40625</v>
+        <v>46167.40625</v>
       </c>
       <c r="B41">
-        <v>0.648</v>
+        <v>10.187</v>
       </c>
       <c r="C41">
-        <v>5.265</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46164.41666666666</v>
+        <v>46167.41666666666</v>
       </c>
       <c r="B42">
-        <v>5.105</v>
+        <v>3.947</v>
       </c>
       <c r="C42">
-        <v>1.287</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46164.42708333334</v>
+        <v>46167.42708333334</v>
       </c>
       <c r="B43">
-        <v>1.296</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>3.595</v>
+        <v>21.786</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46164.4375</v>
+        <v>46167.4375</v>
       </c>
       <c r="B44">
-        <v>22.112</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0.106</v>
+        <v>38.676</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46164.44791666666</v>
+        <v>46167.44791666666</v>
       </c>
       <c r="B45">
-        <v>12.928</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>4.603</v>
+        <v>30.956</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46164.45833333334</v>
+        <v>46167.45833333334</v>
       </c>
       <c r="B46">
-        <v>1.916</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>5.803</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46164.46875</v>
-      </c>
-      <c r="B47">
-        <v>0.732</v>
-      </c>
-      <c r="C47">
-        <v>0.666</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46164.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48">
-        <v>4.275</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46164.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>1.491</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46164.5</v>
-      </c>
-      <c r="B50">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="C50">
-        <v>1.914</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46164.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>5.099</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46164.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>16.996</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46164.53125</v>
-      </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,208 +400,208 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>17.803</v>
+        <v>0.2</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6.673</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
-        <v>10.605</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>13.363</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
-        <v>8.381</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>8.631</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>14.65</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1.698</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>4.432</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>6.336</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>2.368</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>17.299</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>2.524</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>23.273</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>3.283</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>26.623</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>3.366</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.615</v>
+        <v>16.559</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>4.653</v>
+        <v>4.811</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>24.672</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>48.995</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>61.361</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>35.966</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>9.002000000000001</v>
+        <v>11.336</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>9.913</v>
+        <v>29.436</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>5.433</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0.908</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>12.526</v>
+        <v>9.374000000000001</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>16.311</v>
+        <v>7.448</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,287 +609,210 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>5.014</v>
+        <v>7.938</v>
       </c>
       <c r="C21">
-        <v>0.047</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.384</v>
+        <v>19.179</v>
       </c>
       <c r="C22">
-        <v>23.104</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>38.534</v>
       </c>
       <c r="C23">
-        <v>22.383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="C24">
-        <v>26.61</v>
+        <v>23.668</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>24.209</v>
+        <v>27.513</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>47.808</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>5.674</v>
       </c>
       <c r="C27">
-        <v>55.483</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>10.617</v>
       </c>
       <c r="C28">
-        <v>29.503</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>24.394</v>
       </c>
       <c r="C29">
-        <v>13.124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>10.212</v>
       </c>
       <c r="C30">
-        <v>35.495</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.334</v>
+        <v>24.017</v>
       </c>
       <c r="C31">
-        <v>5.635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>6.287</v>
+        <v>19.041</v>
       </c>
       <c r="C32">
-        <v>0.046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>8.635</v>
       </c>
       <c r="C33">
-        <v>7.265</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>8.984</v>
+        <v>5.762</v>
       </c>
       <c r="C34">
-        <v>0.081</v>
+        <v>2.826</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.122</v>
+        <v>6.344</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.363</v>
+        <v>0.769</v>
       </c>
       <c r="C36">
-        <v>1.124</v>
+        <v>4.256</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>2.702</v>
+        <v>0.023</v>
       </c>
       <c r="C37">
-        <v>0.32</v>
+        <v>4.711</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>7.082</v>
+        <v>9.846</v>
       </c>
       <c r="C38">
-        <v>0.051</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>13.94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46167.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>28.867</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46167.40625</v>
-      </c>
-      <c r="B41">
-        <v>10.187</v>
-      </c>
-      <c r="C41">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46167.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>3.947</v>
-      </c>
-      <c r="C42">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46167.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>21.786</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46167.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>38.676</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46167.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>30.956</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46167.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,419 +400,595 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46185</v>
       </c>
       <c r="B2">
-        <v>0.2</v>
+        <v>1.424</v>
       </c>
       <c r="C2">
-        <v>6.673</v>
+        <v>2.954</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="C3">
-        <v>13.363</v>
+        <v>5.774</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="C4">
-        <v>8.631</v>
+        <v>2.283</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C5">
-        <v>1.698</v>
+        <v>10.806</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>6.336</v>
+        <v>8.483000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1.496</v>
       </c>
       <c r="C7">
-        <v>17.299</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="C8">
-        <v>23.273</v>
+        <v>1.998</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.902</v>
       </c>
       <c r="C9">
-        <v>26.623</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1.446</v>
       </c>
       <c r="C10">
-        <v>16.559</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>4.811</v>
+        <v>2.459</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="C12">
-        <v>3.75</v>
+        <v>6.902</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1.497</v>
       </c>
       <c r="C13">
-        <v>0.844</v>
+        <v>6.154</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="C14">
-        <v>3.029</v>
+        <v>5.593</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0.045</v>
+        <v>14.492</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>11.336</v>
+        <v>20.941</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>29.436</v>
+        <v>26.496</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>11.68</v>
+        <v>15.331</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B19">
-        <v>9.374000000000001</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0.03</v>
+        <v>24.875</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B20">
-        <v>7.448</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>20.196</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B21">
-        <v>7.938</v>
+        <v>2.27</v>
       </c>
       <c r="C21">
-        <v>0.004</v>
+        <v>4.332</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B22">
-        <v>19.179</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.011</v>
+        <v>29.269</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B23">
-        <v>38.534</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>14.968</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.46</v>
+        <v>0.031</v>
       </c>
       <c r="C24">
-        <v>23.668</v>
+        <v>9.858000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>3.989</v>
       </c>
       <c r="C25">
-        <v>27.513</v>
+        <v>2.731</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="C26">
-        <v>16.73</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B27">
-        <v>5.674</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="C27">
-        <v>0.413</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B28">
-        <v>10.617</v>
+        <v>15.152</v>
       </c>
       <c r="C28">
-        <v>0.053</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B29">
-        <v>24.394</v>
+        <v>7.164</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2.276</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B30">
-        <v>10.212</v>
+        <v>0.364</v>
       </c>
       <c r="C30">
-        <v>0.114</v>
+        <v>24.935</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B31">
-        <v>24.017</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>15.275</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B32">
-        <v>19.041</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>29.275</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B33">
-        <v>8.635</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.223</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B34">
-        <v>5.762</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>2.826</v>
+        <v>28.687</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>6.344</v>
+        <v>9.042999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.769</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>4.256</v>
+        <v>6.269</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>4.711</v>
+        <v>12.361</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B38">
-        <v>9.846</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.127</v>
+        <v>17.207</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46185.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>4.271</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46185.40625</v>
+      </c>
+      <c r="B41">
+        <v>0.003</v>
+      </c>
+      <c r="C41">
+        <v>5.748</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46185.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>12.561</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46185.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>16.496</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46185.4375</v>
+      </c>
+      <c r="B44">
+        <v>0.908</v>
+      </c>
+      <c r="C44">
+        <v>4.024</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46185.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>8.201000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46185.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>0.042</v>
+      </c>
+      <c r="C46">
+        <v>6.138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46185.46875</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46185.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>0.123</v>
+      </c>
+      <c r="C48">
+        <v>6.026</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46185.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>2.86</v>
+      </c>
+      <c r="C49">
+        <v>1.049</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46185.5</v>
+      </c>
+      <c r="B50">
+        <v>2.06</v>
+      </c>
+      <c r="C50">
+        <v>0.405</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46185.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0.006</v>
+      </c>
+      <c r="C51">
+        <v>11.943</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46185.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>15.76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46185.53125</v>
+      </c>
+      <c r="B53">
+        <v>0.265</v>
+      </c>
+      <c r="C53">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46185.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>31.998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2">
+        <v>46185.5625</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,595 +400,518 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="B2">
-        <v>1.424</v>
+        <v>6.55</v>
       </c>
       <c r="C2">
-        <v>2.954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46185.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.486</v>
+        <v>1.355</v>
       </c>
       <c r="C3">
-        <v>5.774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.136</v>
+        <v>1.803</v>
       </c>
       <c r="C4">
-        <v>2.283</v>
+        <v>3.002</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46185.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
-        <v>0.004</v>
+        <v>0.09</v>
       </c>
       <c r="C5">
-        <v>10.806</v>
+        <v>19.308</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>8.483000000000001</v>
+        <v>28.615</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.496</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>6.6</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46185.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1.998</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.902</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>2.125</v>
+        <v>5.904</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.446</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>6.84</v>
+        <v>7.441</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46185.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C11">
-        <v>2.459</v>
+        <v>7.684</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.053</v>
+        <v>0.658</v>
       </c>
       <c r="C12">
-        <v>6.902</v>
+        <v>25.744</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.497</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>6.154</v>
+        <v>20.679</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46185.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
-        <v>0.245</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>5.593</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="C15">
-        <v>14.492</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.186</v>
       </c>
       <c r="C16">
-        <v>20.941</v>
+        <v>8.632</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46185.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>26.496</v>
+        <v>14.548</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2.047</v>
       </c>
       <c r="C18">
-        <v>15.331</v>
+        <v>6.259</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>10.899</v>
       </c>
       <c r="C19">
-        <v>24.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46185.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>12.575</v>
       </c>
       <c r="C20">
-        <v>20.196</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.27</v>
+        <v>23.701</v>
       </c>
       <c r="C21">
-        <v>4.332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>17.609</v>
       </c>
       <c r="C22">
-        <v>29.269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46185.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>13.489</v>
       </c>
       <c r="C23">
-        <v>14.968</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.031</v>
+        <v>1.135</v>
       </c>
       <c r="C24">
-        <v>9.858000000000001</v>
+        <v>11.358</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B25">
-        <v>3.989</v>
+        <v>0.099</v>
       </c>
       <c r="C25">
-        <v>2.731</v>
+        <v>5.726</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46185.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>6.32</v>
+        <v>2.372</v>
       </c>
       <c r="C26">
-        <v>0.438</v>
+        <v>4.933</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B27">
-        <v>8.507999999999999</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.013</v>
+        <v>13.305</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B28">
-        <v>15.152</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.003</v>
+        <v>26.074</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46185.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>7.164</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>2.276</v>
+        <v>22.222</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.364</v>
+        <v>0.822</v>
       </c>
       <c r="C30">
-        <v>24.935</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="C31">
-        <v>15.275</v>
+        <v>9.311999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46185.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>29.275</v>
+        <v>25.656</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>13.46</v>
+        <v>16.807</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>28.687</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46185.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C35">
-        <v>9.042999999999999</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>16.617</v>
       </c>
       <c r="C36">
-        <v>6.269</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="C37">
-        <v>12.361</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46185.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>8.624000000000001</v>
       </c>
       <c r="C38">
-        <v>17.207</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0.032</v>
+        <v>30.647</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>4.271</v>
+        <v>5.472</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46185.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>5.748</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>12.561</v>
+        <v>1.654</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>16.496</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46185.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>0.908</v>
+        <v>0.232</v>
       </c>
       <c r="C44">
-        <v>4.024</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="C45">
-        <v>8.201000000000001</v>
+        <v>8.045</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46185.45833333334</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.042</v>
+        <v>5.212</v>
       </c>
       <c r="C46">
-        <v>6.138</v>
+        <v>2.583</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46185.46875</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>4.178</v>
       </c>
       <c r="C47">
-        <v>18.2</v>
+        <v>1.322</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46185.47916666666</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>6.026</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46185.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>2.86</v>
-      </c>
-      <c r="C49">
-        <v>1.049</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46185.5</v>
-      </c>
-      <c r="B50">
-        <v>2.06</v>
-      </c>
-      <c r="C50">
-        <v>0.405</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46185.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0.006</v>
-      </c>
-      <c r="C51">
-        <v>11.943</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46185.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>15.76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46185.53125</v>
-      </c>
-      <c r="B53">
-        <v>0.265</v>
-      </c>
-      <c r="C53">
-        <v>13.32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46185.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
-        <v>31.998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
-        <v>46185.5625</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,518 +400,595 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B2">
-        <v>6.55</v>
+        <v>1.365</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2.069</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46213.01041666666</v>
+        <v>46216.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.355</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>4.663</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46213.02083333334</v>
+        <v>46216.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.803</v>
+        <v>0.703</v>
       </c>
       <c r="C4">
-        <v>3.002</v>
+        <v>4.126</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46213.03125</v>
+        <v>46216.03125</v>
       </c>
       <c r="B5">
-        <v>0.09</v>
+        <v>0.001</v>
       </c>
       <c r="C5">
-        <v>19.308</v>
+        <v>13.192</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46213.04166666666</v>
+        <v>46216.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>28.615</v>
+        <v>8.683999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46213.05208333334</v>
+        <v>46216.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>7.96</v>
+        <v>34.23</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46213.0625</v>
+        <v>46216.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>7.05</v>
+        <v>42.932</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46213.07291666666</v>
+        <v>46216.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>5.904</v>
+        <v>16.171</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46213.08333333334</v>
+        <v>46216.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>7.441</v>
+        <v>3.918</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46213.09375</v>
+        <v>46216.09375</v>
       </c>
       <c r="B11">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>7.684</v>
+        <v>2.179</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46213.10416666666</v>
+        <v>46216.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.658</v>
+        <v>7.014</v>
       </c>
       <c r="C12">
-        <v>25.744</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46213.11458333334</v>
+        <v>46216.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>16.02</v>
       </c>
       <c r="C13">
-        <v>20.679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46213.125</v>
+        <v>46216.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>9.205</v>
       </c>
       <c r="C14">
-        <v>7.056</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46213.13541666666</v>
+        <v>46216.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.019</v>
+        <v>28.702</v>
       </c>
       <c r="C15">
-        <v>10.325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46213.14583333334</v>
+        <v>46216.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.186</v>
+        <v>25.544</v>
       </c>
       <c r="C16">
-        <v>8.632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46213.15625</v>
+        <v>46216.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>18.482</v>
       </c>
       <c r="C17">
-        <v>14.548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46213.16666666666</v>
+        <v>46216.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.047</v>
+        <v>4.987</v>
       </c>
       <c r="C18">
-        <v>6.259</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46213.17708333334</v>
+        <v>46216.17708333334</v>
       </c>
       <c r="B19">
-        <v>10.899</v>
+        <v>14.867</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46213.1875</v>
+        <v>46216.1875</v>
       </c>
       <c r="B20">
-        <v>12.575</v>
+        <v>27.525</v>
       </c>
       <c r="C20">
-        <v>0.007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46213.19791666666</v>
+        <v>46216.19791666666</v>
       </c>
       <c r="B21">
-        <v>23.701</v>
+        <v>10.443</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46213.20833333334</v>
+        <v>46216.20833333334</v>
       </c>
       <c r="B22">
-        <v>17.609</v>
+        <v>2.432</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46213.21875</v>
+        <v>46216.21875</v>
       </c>
       <c r="B23">
-        <v>13.489</v>
+        <v>4.247</v>
       </c>
       <c r="C23">
-        <v>0.319</v>
+        <v>1.547</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46213.22916666666</v>
+        <v>46216.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.135</v>
+        <v>0.383</v>
       </c>
       <c r="C24">
-        <v>11.358</v>
+        <v>4.728</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46213.23958333334</v>
+        <v>46216.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.099</v>
+        <v>0.404</v>
       </c>
       <c r="C25">
-        <v>5.726</v>
+        <v>7.903</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46213.25</v>
+        <v>46216.25</v>
       </c>
       <c r="B26">
-        <v>2.372</v>
+        <v>0.012</v>
       </c>
       <c r="C26">
-        <v>4.933</v>
+        <v>8.361000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46213.26041666666</v>
+        <v>46216.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C27">
-        <v>13.305</v>
+        <v>6.574</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46213.27083333334</v>
+        <v>46216.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.638</v>
       </c>
       <c r="C28">
-        <v>26.074</v>
+        <v>4.633</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46213.28125</v>
+        <v>46216.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="C29">
-        <v>22.222</v>
+        <v>4.126</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46213.29166666666</v>
+        <v>46216.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.822</v>
+        <v>0.093</v>
       </c>
       <c r="C30">
-        <v>4.72</v>
+        <v>5.256</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46213.30208333334</v>
+        <v>46216.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.065</v>
+        <v>6.089</v>
       </c>
       <c r="C31">
-        <v>9.311999999999999</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46213.3125</v>
+        <v>46216.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>13.637</v>
       </c>
       <c r="C32">
-        <v>25.656</v>
+        <v>1.344</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46213.32291666666</v>
+        <v>46216.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C33">
-        <v>16.807</v>
+        <v>12.225</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46213.33333333334</v>
+        <v>46216.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1.641</v>
       </c>
       <c r="C34">
-        <v>1.394</v>
+        <v>6.402</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46213.34375</v>
+        <v>46216.34375</v>
       </c>
       <c r="B35">
-        <v>0.016</v>
+        <v>20.927</v>
       </c>
       <c r="C35">
-        <v>0.359</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46213.35416666666</v>
+        <v>46216.35416666666</v>
       </c>
       <c r="B36">
-        <v>16.617</v>
+        <v>4.198</v>
       </c>
       <c r="C36">
-        <v>0.471</v>
+        <v>4.014</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46213.36458333334</v>
+        <v>46216.36458333334</v>
       </c>
       <c r="B37">
-        <v>5.08</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="C37">
-        <v>0.044</v>
+        <v>14.564</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46213.375</v>
+        <v>46216.375</v>
       </c>
       <c r="B38">
-        <v>8.624000000000001</v>
+        <v>7.782</v>
       </c>
       <c r="C38">
-        <v>0.073</v>
+        <v>2.566</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46213.38541666666</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1.921</v>
       </c>
       <c r="C39">
-        <v>30.647</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46213.39583333334</v>
+        <v>46216.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>19.282</v>
       </c>
       <c r="C40">
-        <v>5.472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46213.40625</v>
+        <v>46216.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="C41">
-        <v>7.44</v>
+        <v>4.098</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46213.41666666666</v>
+        <v>46216.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="C42">
-        <v>1.654</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46213.42708333334</v>
+        <v>46216.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>4.619</v>
       </c>
       <c r="C43">
-        <v>1.494</v>
+        <v>1.247</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46213.4375</v>
+        <v>46216.4375</v>
       </c>
       <c r="B44">
-        <v>0.232</v>
+        <v>1.911</v>
       </c>
       <c r="C44">
-        <v>3.771</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46213.44791666666</v>
+        <v>46216.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.519</v>
+        <v>4.48</v>
       </c>
       <c r="C45">
-        <v>8.045</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46213.45833333334</v>
+        <v>46216.45833333334</v>
       </c>
       <c r="B46">
-        <v>5.212</v>
+        <v>0.403</v>
       </c>
       <c r="C46">
-        <v>2.583</v>
+        <v>5.562</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46213.46875</v>
+        <v>46216.46875</v>
       </c>
       <c r="B47">
-        <v>4.178</v>
+        <v>29.234</v>
       </c>
       <c r="C47">
-        <v>1.322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46213.47916666666</v>
+        <v>46216.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>44.937</v>
       </c>
       <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46216.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>52.266</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46216.5</v>
+      </c>
+      <c r="B50">
+        <v>34.385</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46216.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>8.858000000000001</v>
+      </c>
+      <c r="C51">
+        <v>1.319</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46216.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>1.673</v>
+      </c>
+      <c r="C52">
+        <v>1.967</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46216.53125</v>
+      </c>
+      <c r="B53">
+        <v>8.298999999999999</v>
+      </c>
+      <c r="C53">
+        <v>0.5590000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46216.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>17.862</v>
+      </c>
+      <c r="C54">
+        <v>3.694</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2">
+        <v>46216.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,153 +400,153 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>1.365</v>
+        <v>0.012</v>
       </c>
       <c r="C2">
-        <v>2.069</v>
+        <v>32.051</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46216.01041666666</v>
+        <v>46218.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>4.663</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46216.02083333334</v>
+        <v>46218.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.703</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>4.126</v>
+        <v>16.362</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46216.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>13.192</v>
+        <v>22.649</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46216.04166666666</v>
+        <v>46218.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.953</v>
       </c>
       <c r="C6">
-        <v>8.683999999999999</v>
+        <v>1.192</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46216.05208333334</v>
+        <v>46218.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C7">
-        <v>34.23</v>
+        <v>5.767</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46216.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C8">
-        <v>42.932</v>
+        <v>1.005</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46216.07291666666</v>
+        <v>46218.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>16.171</v>
+        <v>3.329</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46216.08333333334</v>
+        <v>46218.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="C10">
-        <v>3.918</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46216.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2.173</v>
       </c>
       <c r="C11">
-        <v>2.179</v>
+        <v>1.781</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46216.10416666666</v>
+        <v>46218.10416666666</v>
       </c>
       <c r="B12">
-        <v>7.014</v>
+        <v>0.457</v>
       </c>
       <c r="C12">
-        <v>0.08699999999999999</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46216.11458333334</v>
+        <v>46218.11458333334</v>
       </c>
       <c r="B13">
-        <v>16.02</v>
+        <v>1.128</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1.609</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46216.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>9.205</v>
+        <v>11.96</v>
       </c>
       <c r="C14">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46216.13541666666</v>
+        <v>46218.13541666666</v>
       </c>
       <c r="B15">
-        <v>28.702</v>
+        <v>16.481</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -554,441 +554,364 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46216.14583333334</v>
+        <v>46218.14583333334</v>
       </c>
       <c r="B16">
-        <v>25.544</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46216.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>18.482</v>
+        <v>5.061</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46216.16666666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="B18">
-        <v>4.987</v>
+        <v>1.89</v>
       </c>
       <c r="C18">
-        <v>0.309</v>
+        <v>5.977</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46216.17708333334</v>
+        <v>46218.17708333334</v>
       </c>
       <c r="B19">
-        <v>14.867</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0.113</v>
+        <v>4.058</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46216.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>27.525</v>
+        <v>6.013</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46216.19791666666</v>
+        <v>46218.19791666666</v>
       </c>
       <c r="B21">
-        <v>10.443</v>
+        <v>8.632999999999999</v>
       </c>
       <c r="C21">
-        <v>0.07000000000000001</v>
+        <v>1.708</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46216.20833333334</v>
+        <v>46218.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.432</v>
+        <v>1.571</v>
       </c>
       <c r="C22">
-        <v>0.081</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46216.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>4.247</v>
+        <v>6.92</v>
       </c>
       <c r="C23">
-        <v>1.547</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46216.22916666666</v>
+        <v>46218.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.383</v>
+        <v>12.518</v>
       </c>
       <c r="C24">
-        <v>4.728</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46216.23958333334</v>
+        <v>46218.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.404</v>
+        <v>26.949</v>
       </c>
       <c r="C25">
-        <v>7.903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46216.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>0.012</v>
+        <v>7.45</v>
       </c>
       <c r="C26">
-        <v>8.361000000000001</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46216.26041666666</v>
+        <v>46218.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.007</v>
+        <v>11.053</v>
       </c>
       <c r="C27">
-        <v>6.574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46216.27083333334</v>
+        <v>46218.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.638</v>
+        <v>29.704</v>
       </c>
       <c r="C28">
-        <v>4.633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46216.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>0.98</v>
+        <v>23.119</v>
       </c>
       <c r="C29">
-        <v>4.126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46216.29166666666</v>
+        <v>46218.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.093</v>
+        <v>36.868</v>
       </c>
       <c r="C30">
-        <v>5.256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46216.30208333334</v>
+        <v>46218.30208333334</v>
       </c>
       <c r="B31">
-        <v>6.089</v>
+        <v>20.768</v>
       </c>
       <c r="C31">
-        <v>0.149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46216.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>13.637</v>
+        <v>11.684</v>
       </c>
       <c r="C32">
-        <v>1.344</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46216.32291666666</v>
+        <v>46218.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.008</v>
+        <v>0.037</v>
       </c>
       <c r="C33">
-        <v>12.225</v>
+        <v>15.848</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46216.33333333334</v>
+        <v>46218.33333333334</v>
       </c>
       <c r="B34">
-        <v>1.641</v>
+        <v>4.377</v>
       </c>
       <c r="C34">
-        <v>6.402</v>
+        <v>1.285</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46216.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>20.927</v>
+        <v>1.508</v>
       </c>
       <c r="C35">
-        <v>0.008999999999999999</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46216.35416666666</v>
+        <v>46218.35416666666</v>
       </c>
       <c r="B36">
-        <v>4.198</v>
+        <v>6.384</v>
       </c>
       <c r="C36">
-        <v>4.014</v>
+        <v>1.744</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46216.36458333334</v>
+        <v>46218.36458333334</v>
       </c>
       <c r="B37">
-        <v>8.026999999999999</v>
+        <v>1.799</v>
       </c>
       <c r="C37">
-        <v>14.564</v>
+        <v>6.614</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46216.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>7.782</v>
+        <v>4.107</v>
       </c>
       <c r="C38">
-        <v>2.566</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46216.38541666666</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="B39">
-        <v>1.921</v>
+        <v>0.184</v>
       </c>
       <c r="C39">
-        <v>0.774</v>
+        <v>4.576</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46216.39583333334</v>
+        <v>46218.39583333334</v>
       </c>
       <c r="B40">
-        <v>19.282</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>4.496</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46216.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
-        <v>1.097</v>
+        <v>0.039</v>
       </c>
       <c r="C41">
-        <v>4.098</v>
+        <v>4.766</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46216.41666666666</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.503</v>
+        <v>5.625</v>
       </c>
       <c r="C42">
-        <v>0.886</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46216.42708333334</v>
+        <v>46218.42708333334</v>
       </c>
       <c r="B43">
-        <v>4.619</v>
+        <v>5.625</v>
       </c>
       <c r="C43">
-        <v>1.247</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46216.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
-        <v>1.911</v>
+        <v>0.04</v>
       </c>
       <c r="C44">
-        <v>11.47</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46216.44791666666</v>
+        <v>46218.44791666666</v>
       </c>
       <c r="B45">
-        <v>4.48</v>
+        <v>0.169</v>
       </c>
       <c r="C45">
-        <v>2.989</v>
+        <v>3.713</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46216.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.403</v>
+        <v>0.122</v>
       </c>
       <c r="C46">
-        <v>5.562</v>
+        <v>9.569000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46216.46875</v>
+        <v>46218.46875</v>
       </c>
       <c r="B47">
-        <v>29.234</v>
+        <v>0.024</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>11.781</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46216.47916666666</v>
+        <v>46218.47916666666</v>
       </c>
       <c r="B48">
-        <v>44.937</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46216.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>52.266</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46216.5</v>
-      </c>
-      <c r="B50">
-        <v>34.385</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46216.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>8.858000000000001</v>
-      </c>
-      <c r="C51">
-        <v>1.319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46216.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>1.673</v>
-      </c>
-      <c r="C52">
-        <v>1.967</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46216.53125</v>
-      </c>
-      <c r="B53">
-        <v>8.298999999999999</v>
-      </c>
-      <c r="C53">
-        <v>0.5590000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46216.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>17.862</v>
-      </c>
-      <c r="C54">
-        <v>3.694</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
-        <v>46216.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,263 +400,263 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B2">
-        <v>0.012</v>
+        <v>1.593</v>
       </c>
       <c r="C2">
-        <v>32.051</v>
+        <v>1.102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46218.01041666666</v>
+        <v>46219.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="C3">
-        <v>24.29</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46218.02083333334</v>
+        <v>46219.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="C4">
-        <v>16.362</v>
+        <v>7.646</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>4.866</v>
       </c>
       <c r="C5">
-        <v>22.649</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46218.04166666666</v>
+        <v>46219.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.953</v>
+        <v>3.537</v>
       </c>
       <c r="C6">
-        <v>1.192</v>
+        <v>4.451</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46218.05208333334</v>
+        <v>46219.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.07000000000000001</v>
+        <v>1.992</v>
       </c>
       <c r="C7">
-        <v>5.767</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B8">
-        <v>0.022</v>
+        <v>4.112</v>
       </c>
       <c r="C8">
-        <v>1.005</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46218.07291666666</v>
+        <v>46219.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>3.257</v>
       </c>
       <c r="C9">
-        <v>3.329</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46218.08333333334</v>
+        <v>46219.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.402</v>
+        <v>5.734</v>
       </c>
       <c r="C10">
-        <v>1.044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B11">
-        <v>2.173</v>
+        <v>2.912</v>
       </c>
       <c r="C11">
-        <v>1.781</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46218.10416666666</v>
+        <v>46219.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.457</v>
+        <v>2.425</v>
       </c>
       <c r="C12">
-        <v>2.87</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46218.11458333334</v>
+        <v>46219.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.128</v>
+        <v>2.647</v>
       </c>
       <c r="C13">
-        <v>1.609</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B14">
-        <v>11.96</v>
+        <v>0.011</v>
       </c>
       <c r="C14">
-        <v>0.008</v>
+        <v>6.689</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46218.13541666666</v>
+        <v>46219.13541666666</v>
       </c>
       <c r="B15">
-        <v>16.481</v>
+        <v>0.107</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2.269</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46218.14583333334</v>
+        <v>46219.14583333334</v>
       </c>
       <c r="B16">
-        <v>9.326000000000001</v>
+        <v>0.152</v>
       </c>
       <c r="C16">
-        <v>0.034</v>
+        <v>2.968</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B17">
-        <v>5.061</v>
+        <v>0.232</v>
       </c>
       <c r="C17">
-        <v>0.874</v>
+        <v>3.856</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46218.16666666666</v>
+        <v>46219.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.89</v>
+        <v>1.226</v>
       </c>
       <c r="C18">
-        <v>5.977</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46218.17708333334</v>
+        <v>46219.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>9.901</v>
       </c>
       <c r="C19">
-        <v>4.058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B20">
-        <v>6.013</v>
+        <v>4.21</v>
       </c>
       <c r="C20">
-        <v>0.3</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46218.19791666666</v>
+        <v>46219.19791666666</v>
       </c>
       <c r="B21">
-        <v>8.632999999999999</v>
+        <v>9.206</v>
       </c>
       <c r="C21">
-        <v>1.708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46218.20833333334</v>
+        <v>46219.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.571</v>
+        <v>20.148</v>
       </c>
       <c r="C22">
-        <v>1.286</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B23">
-        <v>6.92</v>
+        <v>16.584</v>
       </c>
       <c r="C23">
-        <v>0.064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46218.22916666666</v>
+        <v>46219.22916666666</v>
       </c>
       <c r="B24">
-        <v>12.518</v>
+        <v>20.386</v>
       </c>
       <c r="C24">
-        <v>0.317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46218.23958333334</v>
+        <v>46219.23958333334</v>
       </c>
       <c r="B25">
-        <v>26.949</v>
+        <v>20.125</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -664,21 +664,21 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B26">
-        <v>7.45</v>
+        <v>8.725</v>
       </c>
       <c r="C26">
-        <v>0.411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46218.26041666666</v>
+        <v>46219.26041666666</v>
       </c>
       <c r="B27">
-        <v>11.053</v>
+        <v>13.298</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -686,10 +686,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46218.27083333334</v>
+        <v>46219.27083333334</v>
       </c>
       <c r="B28">
-        <v>29.704</v>
+        <v>0.78</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -697,10 +697,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46218.28125</v>
+        <v>46219.28125</v>
       </c>
       <c r="B29">
-        <v>23.119</v>
+        <v>12.426</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -708,10 +708,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46218.29166666666</v>
+        <v>46219.29166666666</v>
       </c>
       <c r="B30">
-        <v>36.868</v>
+        <v>8.597</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -719,10 +719,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46218.30208333334</v>
+        <v>46219.30208333334</v>
       </c>
       <c r="B31">
-        <v>20.768</v>
+        <v>8.597</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -730,188 +730,166 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46218.3125</v>
+        <v>46219.3125</v>
       </c>
       <c r="B32">
-        <v>11.684</v>
+        <v>3.431</v>
       </c>
       <c r="C32">
-        <v>0.17</v>
+        <v>1.462</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46218.32291666666</v>
+        <v>46219.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.037</v>
+        <v>7.007</v>
       </c>
       <c r="C33">
-        <v>15.848</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46218.33333333334</v>
+        <v>46219.33333333334</v>
       </c>
       <c r="B34">
-        <v>4.377</v>
+        <v>6.373</v>
       </c>
       <c r="C34">
-        <v>1.285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46218.34375</v>
+        <v>46219.34375</v>
       </c>
       <c r="B35">
-        <v>1.508</v>
+        <v>6.687</v>
       </c>
       <c r="C35">
-        <v>0.578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46218.35416666666</v>
+        <v>46219.35416666666</v>
       </c>
       <c r="B36">
-        <v>6.384</v>
+        <v>4.545</v>
       </c>
       <c r="C36">
-        <v>1.744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46218.36458333334</v>
+        <v>46219.36458333334</v>
       </c>
       <c r="B37">
-        <v>1.799</v>
+        <v>2.323</v>
       </c>
       <c r="C37">
-        <v>6.614</v>
+        <v>5.513</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46218.375</v>
+        <v>46219.375</v>
       </c>
       <c r="B38">
-        <v>4.107</v>
+        <v>20.482</v>
       </c>
       <c r="C38">
-        <v>0.721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46218.38541666666</v>
+        <v>46219.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.184</v>
+        <v>26.817</v>
       </c>
       <c r="C39">
-        <v>4.576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46218.39583333334</v>
+        <v>46219.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>22.508</v>
       </c>
       <c r="C40">
-        <v>4.496</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B41">
-        <v>0.039</v>
+        <v>1.868</v>
       </c>
       <c r="C41">
-        <v>4.766</v>
+        <v>4.398</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46218.41666666666</v>
+        <v>46219.41666666666</v>
       </c>
       <c r="B42">
-        <v>5.625</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C42">
-        <v>0.696</v>
+        <v>3.751</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46218.42708333334</v>
+        <v>46219.42708333334</v>
       </c>
       <c r="B43">
-        <v>5.625</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.696</v>
+        <v>28.599</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46218.4375</v>
+        <v>46219.4375</v>
       </c>
       <c r="B44">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>1.868</v>
+        <v>14.135</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46218.44791666666</v>
+        <v>46219.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.169</v>
+        <v>0.393</v>
       </c>
       <c r="C45">
-        <v>3.713</v>
+        <v>8.076000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46218.45833333334</v>
+        <v>46219.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>9.569000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46218.46875</v>
-      </c>
-      <c r="B47">
-        <v>0.024</v>
-      </c>
-      <c r="C47">
-        <v>11.781</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46218.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,98 +400,98 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B2">
-        <v>1.593</v>
+        <v>22.938</v>
       </c>
       <c r="C2">
-        <v>1.102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46219.01041666666</v>
+        <v>46223.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.245</v>
+        <v>2.236</v>
       </c>
       <c r="C3">
-        <v>5.428</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46219.02083333334</v>
+        <v>46223.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.223</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>7.646</v>
+        <v>8.144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46219.03125</v>
+        <v>46223.03125</v>
       </c>
       <c r="B5">
-        <v>4.866</v>
+        <v>5.73</v>
       </c>
       <c r="C5">
-        <v>0.073</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46219.04166666666</v>
+        <v>46223.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.537</v>
+        <v>11.331</v>
       </c>
       <c r="C6">
-        <v>4.451</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46219.05208333334</v>
+        <v>46223.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.992</v>
+        <v>23.36</v>
       </c>
       <c r="C7">
-        <v>0.893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46219.0625</v>
+        <v>46223.0625</v>
       </c>
       <c r="B8">
-        <v>4.112</v>
+        <v>11.571</v>
       </c>
       <c r="C8">
-        <v>0.011</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46219.07291666666</v>
+        <v>46223.07291666666</v>
       </c>
       <c r="B9">
-        <v>3.257</v>
+        <v>7.407</v>
       </c>
       <c r="C9">
-        <v>0.464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46219.08333333334</v>
+        <v>46223.08333333334</v>
       </c>
       <c r="B10">
-        <v>5.734</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -499,208 +499,208 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46219.09375</v>
+        <v>46223.09375</v>
       </c>
       <c r="B11">
-        <v>2.912</v>
+        <v>13.465</v>
       </c>
       <c r="C11">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46219.10416666666</v>
+        <v>46223.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.425</v>
+        <v>8.378</v>
       </c>
       <c r="C12">
-        <v>0.584</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46219.11458333334</v>
+        <v>46223.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.647</v>
+        <v>0.479</v>
       </c>
       <c r="C13">
-        <v>9.705</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46219.125</v>
+        <v>46223.125</v>
       </c>
       <c r="B14">
-        <v>0.011</v>
+        <v>0.753</v>
       </c>
       <c r="C14">
-        <v>6.689</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46219.13541666666</v>
+        <v>46223.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>2.269</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46219.14583333334</v>
+        <v>46223.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.152</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C16">
-        <v>2.968</v>
+        <v>4.953</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46219.15625</v>
+        <v>46223.15625</v>
       </c>
       <c r="B17">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>3.856</v>
+        <v>7.444</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46219.16666666666</v>
+        <v>46223.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.226</v>
+        <v>0.063</v>
       </c>
       <c r="C18">
-        <v>0.345</v>
+        <v>2.687</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46219.17708333334</v>
+        <v>46223.17708333334</v>
       </c>
       <c r="B19">
-        <v>9.901</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>19.893</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46219.1875</v>
+        <v>46223.1875</v>
       </c>
       <c r="B20">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.669</v>
+        <v>15.206</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46219.19791666666</v>
+        <v>46223.19791666666</v>
       </c>
       <c r="B21">
-        <v>9.206</v>
+        <v>0.048</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>5.138</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46219.20833333334</v>
+        <v>46223.20833333334</v>
       </c>
       <c r="B22">
-        <v>20.148</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.17</v>
+        <v>16.456</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46219.21875</v>
+        <v>46223.21875</v>
       </c>
       <c r="B23">
-        <v>16.584</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>3.536</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46219.22916666666</v>
+        <v>46223.22916666666</v>
       </c>
       <c r="B24">
-        <v>20.386</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>3.351</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46219.23958333334</v>
+        <v>46223.23958333334</v>
       </c>
       <c r="B25">
-        <v>20.125</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>5.819</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46219.25</v>
+        <v>46223.25</v>
       </c>
       <c r="B26">
-        <v>8.725</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>31.474</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46219.26041666666</v>
+        <v>46223.26041666666</v>
       </c>
       <c r="B27">
-        <v>13.298</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>9.811</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46219.27083333334</v>
+        <v>46223.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.78</v>
+        <v>0.196</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46219.28125</v>
+        <v>46223.28125</v>
       </c>
       <c r="B29">
-        <v>12.426</v>
+        <v>18.517</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -708,188 +708,56 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46219.29166666666</v>
+        <v>46223.29166666666</v>
       </c>
       <c r="B30">
-        <v>8.597</v>
+        <v>15.666</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1.886</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46219.30208333334</v>
+        <v>46223.30208333334</v>
       </c>
       <c r="B31">
-        <v>8.597</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46219.3125</v>
+        <v>46223.3125</v>
       </c>
       <c r="B32">
-        <v>3.431</v>
+        <v>3.027</v>
       </c>
       <c r="C32">
-        <v>1.462</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46219.32291666666</v>
+        <v>46223.32291666666</v>
       </c>
       <c r="B33">
-        <v>7.007</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.159</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46219.33333333334</v>
+        <v>46223.33333333334</v>
       </c>
       <c r="B34">
-        <v>6.373</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
-        <v>46219.34375</v>
-      </c>
-      <c r="B35">
-        <v>6.687</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
-        <v>46219.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>4.545</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
-        <v>46219.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>2.323</v>
-      </c>
-      <c r="C37">
-        <v>5.513</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46219.375</v>
-      </c>
-      <c r="B38">
-        <v>20.482</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46219.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>26.817</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46219.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>22.508</v>
-      </c>
-      <c r="C40">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46219.40625</v>
-      </c>
-      <c r="B41">
-        <v>1.868</v>
-      </c>
-      <c r="C41">
-        <v>4.398</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46219.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="C42">
-        <v>3.751</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46219.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>28.599</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46219.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>14.135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46219.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>0.393</v>
-      </c>
-      <c r="C45">
-        <v>8.076000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46219.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,87 +400,87 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B2">
-        <v>22.938</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46223.01041666666</v>
+        <v>46226.01041666666</v>
       </c>
       <c r="B3">
-        <v>2.236</v>
+        <v>0.214</v>
       </c>
       <c r="C3">
-        <v>0.989</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46223.02083333334</v>
+        <v>46226.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="C4">
-        <v>8.144</v>
+        <v>2.326</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46223.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.285</v>
+        <v>3.738</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46223.04166666666</v>
+        <v>46226.04166666666</v>
       </c>
       <c r="B6">
-        <v>11.331</v>
+        <v>4.102</v>
       </c>
       <c r="C6">
-        <v>0.041</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46223.05208333334</v>
+        <v>46226.05208333334</v>
       </c>
       <c r="B7">
-        <v>23.36</v>
+        <v>6.457</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46223.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
-        <v>11.571</v>
+        <v>30.571</v>
       </c>
       <c r="C8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46223.07291666666</v>
+        <v>46226.07291666666</v>
       </c>
       <c r="B9">
-        <v>7.407</v>
+        <v>19.118</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -488,10 +488,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46223.08333333334</v>
+        <v>46226.08333333334</v>
       </c>
       <c r="B10">
-        <v>8.513999999999999</v>
+        <v>15.025</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -499,10 +499,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46223.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
-        <v>13.465</v>
+        <v>29.124</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -510,254 +510,243 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46223.10416666666</v>
+        <v>46226.10416666666</v>
       </c>
       <c r="B12">
-        <v>8.378</v>
+        <v>37.319</v>
       </c>
       <c r="C12">
-        <v>0.098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46223.11458333334</v>
+        <v>46226.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.479</v>
+        <v>30.632</v>
       </c>
       <c r="C13">
-        <v>2.254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46223.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
-        <v>0.753</v>
+        <v>42.761</v>
       </c>
       <c r="C14">
-        <v>0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46223.13541666666</v>
+        <v>46226.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>21.619</v>
       </c>
       <c r="C15">
-        <v>0.467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46223.14583333334</v>
+        <v>46226.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.008999999999999999</v>
+        <v>3.156</v>
       </c>
       <c r="C16">
-        <v>4.953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46223.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>10.107</v>
       </c>
       <c r="C17">
-        <v>7.444</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46223.16666666666</v>
+        <v>46226.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.063</v>
+        <v>2.612</v>
       </c>
       <c r="C18">
-        <v>2.687</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46223.17708333334</v>
+        <v>46226.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.518</v>
       </c>
       <c r="C19">
-        <v>19.893</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46223.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.823</v>
       </c>
       <c r="C20">
-        <v>15.206</v>
+        <v>1.037</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46223.19791666666</v>
+        <v>46226.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.048</v>
+        <v>2.836</v>
       </c>
       <c r="C21">
-        <v>5.138</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46223.20833333334</v>
+        <v>46226.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2.607</v>
       </c>
       <c r="C22">
-        <v>16.456</v>
+        <v>5.056</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46223.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C23">
-        <v>3.536</v>
+        <v>9.753</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46223.22916666666</v>
+        <v>46226.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="C24">
-        <v>3.351</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46223.23958333334</v>
+        <v>46226.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>10.235</v>
       </c>
       <c r="C25">
-        <v>5.819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46223.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="C26">
-        <v>31.474</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46223.26041666666</v>
+        <v>46226.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="C27">
-        <v>9.811</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46223.27083333334</v>
+        <v>46226.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.196</v>
+        <v>17.669</v>
       </c>
       <c r="C28">
-        <v>4.19</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46223.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>18.517</v>
+        <v>4.272</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1.067</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46223.29166666666</v>
+        <v>46226.29166666666</v>
       </c>
       <c r="B30">
-        <v>15.666</v>
+        <v>0.003</v>
       </c>
       <c r="C30">
-        <v>1.886</v>
+        <v>5.559</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46223.30208333334</v>
+        <v>46226.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.8129999999999999</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>2.624</v>
+        <v>10.657</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46223.3125</v>
+        <v>46226.3125</v>
       </c>
       <c r="B32">
-        <v>3.027</v>
+        <v>0.124</v>
       </c>
       <c r="C32">
-        <v>1.345</v>
+        <v>3.007</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46223.32291666666</v>
+        <v>46226.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>11.34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2">
-        <v>46223.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,353 +400,364 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4.809</v>
       </c>
       <c r="C2">
-        <v>4.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46226.01041666666</v>
+        <v>46227.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.214</v>
+        <v>8.647</v>
       </c>
       <c r="C3">
-        <v>0.787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46226.02083333334</v>
+        <v>46227.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.019</v>
+        <v>4.427</v>
       </c>
       <c r="C4">
-        <v>2.326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="C5">
-        <v>3.738</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46226.04166666666</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="B6">
-        <v>4.102</v>
+        <v>0.57</v>
       </c>
       <c r="C6">
-        <v>0.163</v>
+        <v>3.539</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46226.05208333334</v>
+        <v>46227.05208333334</v>
       </c>
       <c r="B7">
-        <v>6.457</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.097</v>
+        <v>5.696</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
       <c r="B8">
-        <v>30.571</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>10.106</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46226.07291666666</v>
+        <v>46227.07291666666</v>
       </c>
       <c r="B9">
-        <v>19.118</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46226.08333333334</v>
+        <v>46227.08333333334</v>
       </c>
       <c r="B10">
-        <v>15.025</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>10.575</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
       <c r="B11">
-        <v>29.124</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46226.10416666666</v>
+        <v>46227.10416666666</v>
       </c>
       <c r="B12">
-        <v>37.319</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>5.751</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46226.11458333334</v>
+        <v>46227.11458333334</v>
       </c>
       <c r="B13">
-        <v>30.632</v>
+        <v>0.785</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
       <c r="B14">
-        <v>42.761</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>7.327</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46226.13541666666</v>
+        <v>46227.13541666666</v>
       </c>
       <c r="B15">
-        <v>21.619</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>21.973</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46226.14583333334</v>
+        <v>46227.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.156</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
       <c r="B17">
-        <v>10.107</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.004</v>
+        <v>1.275</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46226.16666666666</v>
+        <v>46227.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.612</v>
+        <v>5.161</v>
       </c>
       <c r="C18">
-        <v>0.217</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46226.17708333334</v>
+        <v>46227.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.518</v>
+        <v>4.516</v>
       </c>
       <c r="C19">
-        <v>2.535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
       <c r="B20">
-        <v>0.823</v>
+        <v>3.194</v>
       </c>
       <c r="C20">
-        <v>1.037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46226.19791666666</v>
+        <v>46227.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.836</v>
+        <v>6.915</v>
       </c>
       <c r="C21">
-        <v>0.259</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46226.20833333334</v>
+        <v>46227.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.607</v>
+        <v>0.005</v>
       </c>
       <c r="C22">
-        <v>5.056</v>
+        <v>8.691000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
       <c r="B23">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>9.753</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46226.22916666666</v>
+        <v>46227.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.247</v>
+        <v>7.374</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46226.23958333334</v>
+        <v>46227.23958333334</v>
       </c>
       <c r="B25">
-        <v>10.235</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2.596</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
       <c r="B26">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>1.248</v>
+        <v>19.036</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46226.26041666666</v>
+        <v>46227.26041666666</v>
       </c>
       <c r="B27">
-        <v>6.31</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.157</v>
+        <v>18.637</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46226.27083333334</v>
+        <v>46227.27083333334</v>
       </c>
       <c r="B28">
-        <v>17.669</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.001</v>
+        <v>3.336</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
       <c r="B29">
-        <v>4.272</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>1.067</v>
+        <v>10.656</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46226.29166666666</v>
+        <v>46227.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.003</v>
+        <v>0.137</v>
       </c>
       <c r="C30">
-        <v>5.559</v>
+        <v>8.569000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46226.30208333334</v>
+        <v>46227.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>10.657</v>
+        <v>10.973</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46226.3125</v>
+        <v>46227.3125</v>
       </c>
       <c r="B32">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>3.007</v>
+        <v>15.082</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46226.32291666666</v>
+        <v>46227.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
+        <v>17.938</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2">
+        <v>46227.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,364 +400,375 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B2">
-        <v>4.809</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>9.750999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46227.01041666666</v>
+        <v>46229.01041666666</v>
       </c>
       <c r="B3">
-        <v>8.647</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>2.439</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46227.02083333334</v>
+        <v>46229.02083333334</v>
       </c>
       <c r="B4">
-        <v>4.427</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
       <c r="B5">
-        <v>0.291</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.13</v>
+        <v>36.668</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46227.04166666666</v>
+        <v>46229.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>3.539</v>
+        <v>31.206</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46227.05208333334</v>
+        <v>46229.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>5.696</v>
+        <v>24.729</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>10.106</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46227.07291666666</v>
+        <v>46229.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.594</v>
+        <v>4.106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46227.08333333334</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>10.575</v>
+        <v>3.089</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>7.48</v>
+        <v>12.963</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46227.10416666666</v>
+        <v>46229.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>5.751</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46227.11458333334</v>
+        <v>46229.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.785</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.173</v>
+        <v>4.489</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>7.327</v>
+        <v>12.399</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46227.13541666666</v>
+        <v>46229.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>21.973</v>
+        <v>10.553</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46227.14583333334</v>
+        <v>46229.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>2.45</v>
+        <v>4.858</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.662</v>
       </c>
       <c r="C17">
-        <v>1.275</v>
+        <v>3.656</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46227.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="B18">
-        <v>5.161</v>
+        <v>0.039</v>
       </c>
       <c r="C18">
-        <v>0.184</v>
+        <v>5.737</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46227.17708333334</v>
+        <v>46229.17708333334</v>
       </c>
       <c r="B19">
-        <v>4.516</v>
+        <v>8.542</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
       <c r="B20">
-        <v>3.194</v>
+        <v>7.277</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46227.19791666666</v>
+        <v>46229.19791666666</v>
       </c>
       <c r="B21">
-        <v>6.915</v>
+        <v>4.95</v>
       </c>
       <c r="C21">
-        <v>0.006</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46227.20833333334</v>
+        <v>46229.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.005</v>
+        <v>4.531</v>
       </c>
       <c r="C22">
-        <v>8.691000000000001</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>5.501</v>
       </c>
       <c r="C23">
-        <v>14.44</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46227.22916666666</v>
+        <v>46229.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1.735</v>
       </c>
       <c r="C24">
-        <v>7.374</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46227.23958333334</v>
+        <v>46229.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C25">
-        <v>2.596</v>
+        <v>3.175</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>6.407</v>
       </c>
       <c r="C26">
-        <v>19.036</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46227.26041666666</v>
+        <v>46229.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2.729</v>
       </c>
       <c r="C27">
-        <v>18.637</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46227.27083333334</v>
+        <v>46229.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C28">
-        <v>3.336</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="C29">
-        <v>10.656</v>
+        <v>14.589</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46227.29166666666</v>
+        <v>46229.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.137</v>
+        <v>2.87</v>
       </c>
       <c r="C30">
-        <v>8.569000000000001</v>
+        <v>7.671</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46227.30208333334</v>
+        <v>46229.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>3.717</v>
       </c>
       <c r="C31">
-        <v>10.973</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>2.299</v>
       </c>
       <c r="C32">
-        <v>15.082</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46227.32291666666</v>
+        <v>46229.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>17.938</v>
+        <v>5.745</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46227.33333333334</v>
+        <v>46229.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>7.408</v>
       </c>
       <c r="C34">
+        <v>0.549</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>46229.34375</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,375 +400,628 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4.428</v>
       </c>
       <c r="C2">
-        <v>9.750999999999999</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46229.01041666666</v>
+        <v>46246.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>4.896</v>
       </c>
       <c r="C3">
-        <v>2.439</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46229.02083333334</v>
+        <v>46246.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1.144</v>
       </c>
       <c r="C4">
-        <v>0.49</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C5">
-        <v>36.668</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46229.04166666666</v>
+        <v>46246.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>31.206</v>
+        <v>4.845</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46229.05208333334</v>
+        <v>46246.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>24.729</v>
+        <v>14.652</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>13.99</v>
+        <v>35.979</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46229.07291666666</v>
+        <v>46246.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>4.106</v>
+        <v>57.72</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46229.08333333334</v>
+        <v>46246.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>3.089</v>
+        <v>33.875</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>12.963</v>
+        <v>34.305</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46229.10416666666</v>
+        <v>46246.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="C12">
-        <v>14.69</v>
+        <v>12.531</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46229.11458333334</v>
+        <v>46246.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1.257</v>
       </c>
       <c r="C13">
-        <v>4.489</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1.672</v>
       </c>
       <c r="C14">
-        <v>12.399</v>
+        <v>1.347</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46229.13541666666</v>
+        <v>46246.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1.204</v>
       </c>
       <c r="C15">
-        <v>10.553</v>
+        <v>8.564</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46229.14583333334</v>
+        <v>46246.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.924</v>
       </c>
       <c r="C16">
-        <v>4.858</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
       <c r="B17">
-        <v>0.662</v>
+        <v>4.938</v>
       </c>
       <c r="C17">
-        <v>3.656</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46229.16666666666</v>
+        <v>46246.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.039</v>
+        <v>1.342</v>
       </c>
       <c r="C18">
-        <v>5.737</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46229.17708333334</v>
+        <v>46246.17708333334</v>
       </c>
       <c r="B19">
-        <v>8.542</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0.032</v>
+        <v>27.131</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
       <c r="B20">
-        <v>7.277</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.002</v>
+        <v>43.707</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46229.19791666666</v>
+        <v>46246.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0.119</v>
+        <v>32.849</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46229.20833333334</v>
+        <v>46246.20833333334</v>
       </c>
       <c r="B22">
-        <v>4.531</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.309</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
       <c r="B23">
-        <v>5.501</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0.177</v>
+        <v>30.942</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46229.22916666666</v>
+        <v>46246.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.735</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.23</v>
+        <v>43.847</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46229.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>3.175</v>
+        <v>34.623</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
       <c r="B26">
-        <v>6.407</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.1</v>
+        <v>24.71</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46229.26041666666</v>
+        <v>46246.26041666666</v>
       </c>
       <c r="B27">
-        <v>2.729</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.212</v>
+        <v>26.494</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46229.27083333334</v>
+        <v>46246.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.5600000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="C28">
-        <v>2.576</v>
+        <v>6.603</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
       <c r="B29">
-        <v>0.063</v>
+        <v>4.649</v>
       </c>
       <c r="C29">
-        <v>14.589</v>
+        <v>1.179</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46229.29166666666</v>
+        <v>46246.29166666666</v>
       </c>
       <c r="B30">
-        <v>2.87</v>
+        <v>8.866</v>
       </c>
       <c r="C30">
-        <v>7.671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46229.30208333334</v>
+        <v>46246.30208333334</v>
       </c>
       <c r="B31">
-        <v>3.717</v>
+        <v>0.49</v>
       </c>
       <c r="C31">
-        <v>0.93</v>
+        <v>6.705</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
       <c r="B32">
-        <v>2.299</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>2.86</v>
+        <v>17.832</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46229.32291666666</v>
+        <v>46246.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>5.745</v>
+        <v>10.764</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46229.33333333334</v>
+        <v>46246.33333333334</v>
       </c>
       <c r="B34">
-        <v>7.408</v>
+        <v>0.855</v>
       </c>
       <c r="C34">
-        <v>0.549</v>
+        <v>10.547</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46229.34375</v>
+        <v>46246.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>10.941</v>
       </c>
       <c r="C35">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>46246.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>22.701</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>46246.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>40.288</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>46246.375</v>
+      </c>
+      <c r="B38">
+        <v>29</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>46246.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>7.286</v>
+      </c>
+      <c r="C39">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46246.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>4.063</v>
+      </c>
+      <c r="C40">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46246.40625</v>
+      </c>
+      <c r="B41">
+        <v>0.341</v>
+      </c>
+      <c r="C41">
+        <v>1.242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46246.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>36.806</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46246.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>21.314</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46246.4375</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46246.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>3.657</v>
+      </c>
+      <c r="C45">
+        <v>0.101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46246.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>11.341</v>
+      </c>
+      <c r="C46">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46246.46875</v>
+      </c>
+      <c r="B47">
+        <v>6.343</v>
+      </c>
+      <c r="C47">
+        <v>0.371</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46246.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>1.562</v>
+      </c>
+      <c r="C48">
+        <v>0.397</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46246.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="C49">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46246.5</v>
+      </c>
+      <c r="B50">
+        <v>0.004</v>
+      </c>
+      <c r="C50">
+        <v>1.248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46246.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0.733</v>
+      </c>
+      <c r="C51">
+        <v>2.576</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46246.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>5.341</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46246.53125</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46246.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2">
+        <v>46246.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>4.652</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="2">
+        <v>46246.5625</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>3.065</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="2">
+        <v>46246.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>4.849</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="2">
+        <v>46246.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,318 +400,318 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B2">
-        <v>4.428</v>
+        <v>7.597</v>
       </c>
       <c r="C2">
-        <v>0.428</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46246.01041666666</v>
+        <v>46252.01041666666</v>
       </c>
       <c r="B3">
-        <v>4.896</v>
+        <v>16.206</v>
       </c>
       <c r="C3">
-        <v>0.054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46246.02083333334</v>
+        <v>46252.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.144</v>
+        <v>13.02</v>
       </c>
       <c r="C4">
-        <v>0.463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46246.03125</v>
+        <v>46252.03125</v>
       </c>
       <c r="B5">
-        <v>0.011</v>
+        <v>27.896</v>
       </c>
       <c r="C5">
-        <v>4.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46246.04166666666</v>
+        <v>46252.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="C6">
-        <v>4.845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46246.05208333334</v>
+        <v>46252.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>7.579</v>
       </c>
       <c r="C7">
-        <v>14.652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46246.0625</v>
+        <v>46252.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1.634</v>
       </c>
       <c r="C8">
-        <v>35.979</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46246.07291666666</v>
+        <v>46252.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2.047</v>
       </c>
       <c r="C9">
-        <v>57.72</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46246.08333333334</v>
+        <v>46252.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2.895</v>
       </c>
       <c r="C10">
-        <v>33.875</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46246.09375</v>
+        <v>46252.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="C11">
-        <v>34.305</v>
+        <v>2.927</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46246.10416666666</v>
+        <v>46252.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.059</v>
+        <v>0.835</v>
       </c>
       <c r="C12">
-        <v>12.531</v>
+        <v>1.241</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46246.11458333334</v>
+        <v>46252.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.257</v>
+        <v>0.152</v>
       </c>
       <c r="C13">
-        <v>3.014</v>
+        <v>1.601</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46246.125</v>
+        <v>46252.125</v>
       </c>
       <c r="B14">
-        <v>1.672</v>
+        <v>2.97</v>
       </c>
       <c r="C14">
-        <v>1.347</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46246.13541666666</v>
+        <v>46252.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.204</v>
+        <v>5.116</v>
       </c>
       <c r="C15">
-        <v>8.564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46246.14583333334</v>
+        <v>46252.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.924</v>
+        <v>4.743</v>
       </c>
       <c r="C16">
-        <v>0.386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46246.15625</v>
+        <v>46252.15625</v>
       </c>
       <c r="B17">
-        <v>4.938</v>
+        <v>7.701</v>
       </c>
       <c r="C17">
-        <v>0.101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46246.16666666666</v>
+        <v>46252.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.342</v>
+        <v>11.542</v>
       </c>
       <c r="C18">
-        <v>1.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46246.17708333334</v>
+        <v>46252.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>10.037</v>
       </c>
       <c r="C19">
-        <v>27.131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46246.1875</v>
+        <v>46252.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>8.756</v>
       </c>
       <c r="C20">
-        <v>43.707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46246.19791666666</v>
+        <v>46252.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>8.904</v>
       </c>
       <c r="C21">
-        <v>32.849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46246.20833333334</v>
+        <v>46252.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="C22">
-        <v>22.9</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46246.21875</v>
+        <v>46252.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>5.899</v>
       </c>
       <c r="C23">
-        <v>30.942</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46246.22916666666</v>
+        <v>46252.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1.764</v>
       </c>
       <c r="C24">
-        <v>43.847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46246.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1.349</v>
       </c>
       <c r="C25">
-        <v>34.623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46246.25</v>
+        <v>46252.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="C26">
-        <v>24.71</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46246.26041666666</v>
+        <v>46252.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C27">
-        <v>26.494</v>
+        <v>6.176</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46246.27083333334</v>
+        <v>46252.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.081</v>
+        <v>11.492</v>
       </c>
       <c r="C28">
-        <v>6.603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46246.28125</v>
+        <v>46252.28125</v>
       </c>
       <c r="B29">
-        <v>4.649</v>
+        <v>16.614</v>
       </c>
       <c r="C29">
-        <v>1.179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46246.29166666666</v>
+        <v>46252.29166666666</v>
       </c>
       <c r="B30">
-        <v>8.866</v>
+        <v>8.351000000000001</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -719,309 +719,100 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46246.30208333334</v>
+        <v>46252.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.49</v>
+        <v>16.839</v>
       </c>
       <c r="C31">
-        <v>6.705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46246.3125</v>
+        <v>46252.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>4.509</v>
       </c>
       <c r="C32">
-        <v>17.832</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46246.32291666666</v>
+        <v>46252.33333333334</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1.082</v>
       </c>
       <c r="C33">
-        <v>10.764</v>
+        <v>16.305</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46246.33333333334</v>
+        <v>46252.34375</v>
       </c>
       <c r="B34">
-        <v>0.855</v>
+        <v>10.422</v>
       </c>
       <c r="C34">
-        <v>10.547</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46246.34375</v>
+        <v>46252.35416666666</v>
       </c>
       <c r="B35">
-        <v>10.941</v>
+        <v>1.413</v>
       </c>
       <c r="C35">
-        <v>0.058</v>
+        <v>4.398</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46246.35416666666</v>
+        <v>46252.36458333334</v>
       </c>
       <c r="B36">
-        <v>22.701</v>
+        <v>0.783</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46246.36458333334</v>
+        <v>46252.375</v>
       </c>
       <c r="B37">
-        <v>40.288</v>
+        <v>3.515</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46246.375</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="B38">
-        <v>29</v>
+        <v>3.018</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46246.38541666666</v>
+        <v>46252.39583333334</v>
       </c>
       <c r="B39">
-        <v>7.286</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46246.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>4.063</v>
-      </c>
-      <c r="C40">
-        <v>0.144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46246.40625</v>
-      </c>
-      <c r="B41">
-        <v>0.341</v>
-      </c>
-      <c r="C41">
-        <v>1.242</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46246.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>36.806</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46246.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>21.314</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46246.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46246.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>3.657</v>
-      </c>
-      <c r="C45">
-        <v>0.101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46246.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>11.341</v>
-      </c>
-      <c r="C46">
-        <v>0.229</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46246.46875</v>
-      </c>
-      <c r="B47">
-        <v>6.343</v>
-      </c>
-      <c r="C47">
-        <v>0.371</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46246.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>1.562</v>
-      </c>
-      <c r="C48">
-        <v>0.397</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46246.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="C49">
-        <v>0.251</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46246.5</v>
-      </c>
-      <c r="B50">
-        <v>0.004</v>
-      </c>
-      <c r="C50">
-        <v>1.248</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46246.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0.733</v>
-      </c>
-      <c r="C51">
-        <v>2.576</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46246.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>5.341</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46246.53125</v>
-      </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
-        <v>3.535</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46246.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
-        <v>46246.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>4.652</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="2">
-        <v>46246.5625</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
-        <v>3.065</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="2">
-        <v>46246.57291666666</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57">
-        <v>4.849</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="2">
-        <v>46246.58333333334</v>
-      </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="C58">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,153 +400,153 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B2">
-        <v>7.597</v>
+        <v>3.684</v>
       </c>
       <c r="C2">
-        <v>0.025</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46252.01041666666</v>
+        <v>46259.01041666666</v>
       </c>
       <c r="B3">
-        <v>16.206</v>
+        <v>0.171</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>21.259</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46252.02083333334</v>
+        <v>46259.02083333334</v>
       </c>
       <c r="B4">
-        <v>13.02</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46252.03125</v>
+        <v>46259.03125</v>
       </c>
       <c r="B5">
-        <v>27.896</v>
+        <v>0.972</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46252.04166666666</v>
+        <v>46259.04166666666</v>
       </c>
       <c r="B6">
-        <v>8.861000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46252.05208333334</v>
+        <v>46259.05208333334</v>
       </c>
       <c r="B7">
-        <v>7.579</v>
+        <v>0.881</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>4.352</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46252.0625</v>
+        <v>46259.0625</v>
       </c>
       <c r="B8">
-        <v>1.634</v>
+        <v>17.443</v>
       </c>
       <c r="C8">
-        <v>0.005</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46252.07291666666</v>
+        <v>46259.07291666666</v>
       </c>
       <c r="B9">
-        <v>2.047</v>
+        <v>20.037</v>
       </c>
       <c r="C9">
-        <v>0.041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46252.08333333334</v>
+        <v>46259.08333333334</v>
       </c>
       <c r="B10">
-        <v>2.895</v>
+        <v>19.731</v>
       </c>
       <c r="C10">
-        <v>0.854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46252.09375</v>
+        <v>46259.09375</v>
       </c>
       <c r="B11">
-        <v>0.18</v>
+        <v>3.766</v>
       </c>
       <c r="C11">
-        <v>2.927</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46252.10416666666</v>
+        <v>46259.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.835</v>
+        <v>0.907</v>
       </c>
       <c r="C12">
-        <v>1.241</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46252.11458333334</v>
+        <v>46259.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.152</v>
+        <v>10.954</v>
       </c>
       <c r="C13">
-        <v>1.601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46252.125</v>
+        <v>46259.125</v>
       </c>
       <c r="B14">
-        <v>2.97</v>
+        <v>5.761</v>
       </c>
       <c r="C14">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46252.13541666666</v>
+        <v>46259.13541666666</v>
       </c>
       <c r="B15">
-        <v>5.116</v>
+        <v>16.456</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -554,10 +554,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46252.14583333334</v>
+        <v>46259.14583333334</v>
       </c>
       <c r="B16">
-        <v>4.743</v>
+        <v>37.294</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -565,43 +565,43 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46252.15625</v>
+        <v>46259.15625</v>
       </c>
       <c r="B17">
-        <v>7.701</v>
+        <v>3.751</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46252.16666666666</v>
+        <v>46259.16666666666</v>
       </c>
       <c r="B18">
-        <v>11.542</v>
+        <v>0.929</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1.926</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46252.17708333334</v>
+        <v>46259.17708333334</v>
       </c>
       <c r="B19">
-        <v>10.037</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46252.1875</v>
+        <v>46259.1875</v>
       </c>
       <c r="B20">
-        <v>8.756</v>
+        <v>23.896</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46252.19791666666</v>
+        <v>46259.19791666666</v>
       </c>
       <c r="B21">
-        <v>8.904</v>
+        <v>13.996</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,199 +620,133 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46252.20833333334</v>
+        <v>46259.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.86</v>
+        <v>0.757</v>
       </c>
       <c r="C22">
-        <v>0.366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46252.21875</v>
+        <v>46259.21875</v>
       </c>
       <c r="B23">
-        <v>5.899</v>
+        <v>0.021</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>14.073</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46252.22916666666</v>
+        <v>46259.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.764</v>
+        <v>0.002</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>9.836</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46252.23958333334</v>
+        <v>46259.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.349</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>14.288</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46252.25</v>
+        <v>46259.25</v>
       </c>
       <c r="B26">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>16.54</v>
+        <v>35.842</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46252.26041666666</v>
+        <v>46259.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>6.176</v>
+        <v>75.91800000000001</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46252.27083333334</v>
+        <v>46259.27083333334</v>
       </c>
       <c r="B28">
-        <v>11.492</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>114.634</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46252.28125</v>
+        <v>46259.28125</v>
       </c>
       <c r="B29">
-        <v>16.614</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100.252</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46252.29166666666</v>
+        <v>46259.29166666666</v>
       </c>
       <c r="B30">
-        <v>8.351000000000001</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>75.78700000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46252.30208333334</v>
+        <v>46259.30208333334</v>
       </c>
       <c r="B31">
-        <v>16.839</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>73.06100000000001</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46252.3125</v>
+        <v>46259.3125</v>
       </c>
       <c r="B32">
-        <v>4.509</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1.415</v>
+        <v>28.061</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46252.33333333334</v>
+        <v>46259.32291666666</v>
       </c>
       <c r="B33">
-        <v>1.082</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>16.305</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2">
-        <v>46252.34375</v>
-      </c>
-      <c r="B34">
-        <v>10.422</v>
-      </c>
-      <c r="C34">
-        <v>0.517</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
-        <v>46252.35416666666</v>
-      </c>
-      <c r="B35">
-        <v>1.413</v>
-      </c>
-      <c r="C35">
-        <v>4.398</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
-        <v>46252.36458333334</v>
-      </c>
-      <c r="B36">
-        <v>0.783</v>
-      </c>
-      <c r="C36">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
-        <v>46252.375</v>
-      </c>
-      <c r="B37">
-        <v>3.515</v>
-      </c>
-      <c r="C37">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46252.38541666666</v>
-      </c>
-      <c r="B38">
-        <v>3.018</v>
-      </c>
-      <c r="C38">
-        <v>0.123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46252.39583333334</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,208 +400,208 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B2">
-        <v>3.684</v>
+        <v>1.215</v>
       </c>
       <c r="C2">
-        <v>0.07199999999999999</v>
+        <v>3.172</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46259.01041666666</v>
+        <v>46262.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.171</v>
+        <v>13.961</v>
       </c>
       <c r="C3">
-        <v>21.259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46259.02083333334</v>
+        <v>46262.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>8.087999999999999</v>
       </c>
       <c r="C4">
-        <v>10.196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46259.03125</v>
+        <v>46262.03125</v>
       </c>
       <c r="B5">
-        <v>0.972</v>
+        <v>15.49</v>
       </c>
       <c r="C5">
-        <v>1.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46259.04166666666</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.007</v>
+        <v>5.085</v>
       </c>
       <c r="C6">
-        <v>9.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46259.05208333334</v>
+        <v>46262.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.881</v>
+        <v>3.033</v>
       </c>
       <c r="C7">
-        <v>4.352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46259.0625</v>
+        <v>46262.0625</v>
       </c>
       <c r="B8">
-        <v>17.443</v>
+        <v>0.82</v>
       </c>
       <c r="C8">
-        <v>0.821</v>
+        <v>1.053</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46259.07291666666</v>
+        <v>46262.07291666666</v>
       </c>
       <c r="B9">
-        <v>20.037</v>
+        <v>1.257</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3.181</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46259.08333333334</v>
+        <v>46262.08333333334</v>
       </c>
       <c r="B10">
-        <v>19.731</v>
+        <v>0.158</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>9.577</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46259.09375</v>
+        <v>46262.09375</v>
       </c>
       <c r="B11">
-        <v>3.766</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.736</v>
+        <v>11.815</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46259.10416666666</v>
+        <v>46262.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.907</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.296</v>
+        <v>14.316</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46259.11458333334</v>
+        <v>46262.11458333334</v>
       </c>
       <c r="B13">
-        <v>10.954</v>
+        <v>0.09</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>7.115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46259.125</v>
+        <v>46262.125</v>
       </c>
       <c r="B14">
-        <v>5.761</v>
+        <v>0.272</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2.307</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46259.13541666666</v>
+        <v>46262.13541666666</v>
       </c>
       <c r="B15">
-        <v>16.456</v>
+        <v>0.318</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46259.14583333334</v>
+        <v>46262.14583333334</v>
       </c>
       <c r="B16">
-        <v>37.294</v>
+        <v>0.011</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>6.384</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46259.15625</v>
+        <v>46262.15625</v>
       </c>
       <c r="B17">
-        <v>3.751</v>
+        <v>1.712</v>
       </c>
       <c r="C17">
-        <v>0.149</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46259.16666666666</v>
+        <v>46262.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.929</v>
+        <v>3.109</v>
       </c>
       <c r="C18">
-        <v>1.926</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46259.17708333334</v>
+        <v>46262.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.6899999999999999</v>
+        <v>15.287</v>
       </c>
       <c r="C19">
-        <v>0.599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46259.1875</v>
+        <v>46262.1875</v>
       </c>
       <c r="B20">
-        <v>23.896</v>
+        <v>25.288</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46259.19791666666</v>
+        <v>46262.19791666666</v>
       </c>
       <c r="B21">
-        <v>13.996</v>
+        <v>28.898</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,10 +620,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46259.20833333334</v>
+        <v>46262.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.757</v>
+        <v>14.297</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -631,122 +631,342 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46259.21875</v>
+        <v>46262.21875</v>
       </c>
       <c r="B23">
-        <v>0.021</v>
+        <v>3.872</v>
       </c>
       <c r="C23">
-        <v>14.073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46259.22916666666</v>
+        <v>46262.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.002</v>
+        <v>0.19</v>
       </c>
       <c r="C24">
-        <v>9.836</v>
+        <v>2.807</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46259.23958333334</v>
+        <v>46262.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>14.288</v>
+        <v>6.836</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46259.25</v>
+        <v>46262.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>35.842</v>
+        <v>18.986</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46259.26041666666</v>
+        <v>46262.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C27">
-        <v>75.91800000000001</v>
+        <v>13.233</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46259.27083333334</v>
+        <v>46262.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="C28">
-        <v>114.634</v>
+        <v>3.245</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46259.28125</v>
+        <v>46262.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="C29">
-        <v>100.252</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46259.29166666666</v>
+        <v>46262.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>21.089</v>
       </c>
       <c r="C30">
-        <v>75.78700000000001</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46259.30208333334</v>
+        <v>46262.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>12.59</v>
       </c>
       <c r="C31">
-        <v>73.06100000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46259.3125</v>
+        <v>46262.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>3.523</v>
       </c>
       <c r="C32">
-        <v>28.061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46259.32291666666</v>
+        <v>46262.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.852</v>
       </c>
       <c r="C33">
+        <v>10.381</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2">
+        <v>46262.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>0.063</v>
+      </c>
+      <c r="C34">
+        <v>26.787</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>46262.34375</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>30.769</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>46262.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>0.447</v>
+      </c>
+      <c r="C36">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>46262.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>55.446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>46262.375</v>
+      </c>
+      <c r="B38">
+        <v>1.236</v>
+      </c>
+      <c r="C38">
+        <v>23.365</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>46262.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>0.054</v>
+      </c>
+      <c r="C39">
+        <v>6.571</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46262.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>1.431</v>
+      </c>
+      <c r="C40">
+        <v>1.701</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46262.40625</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0.228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46262.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>2.351</v>
+      </c>
+      <c r="C42">
+        <v>4.601</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46262.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0.003</v>
+      </c>
+      <c r="C43">
+        <v>10.211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46262.4375</v>
+      </c>
+      <c r="B44">
+        <v>0.034</v>
+      </c>
+      <c r="C44">
+        <v>21.765</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46262.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>39.855</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46262.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>34.695</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46262.46875</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>17.602</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46262.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>15.776</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46262.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>10.001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46262.5</v>
+      </c>
+      <c r="B50">
+        <v>6.636</v>
+      </c>
+      <c r="C50">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46262.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0.324</v>
+      </c>
+      <c r="C51">
+        <v>12.982</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46262.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0.544</v>
+      </c>
+      <c r="C52">
+        <v>8.667999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46262.53125</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,21 +400,21 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B2">
-        <v>1.215</v>
+        <v>8.952</v>
       </c>
       <c r="C2">
-        <v>3.172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46262.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
       <c r="B3">
-        <v>13.961</v>
+        <v>14.387</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -422,32 +422,32 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46262.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
       <c r="B4">
-        <v>8.087999999999999</v>
+        <v>3.347</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46262.03125</v>
+        <v>46269.03125</v>
       </c>
       <c r="B5">
-        <v>15.49</v>
+        <v>7.707</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46262.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
       <c r="B6">
-        <v>5.085</v>
+        <v>3.574</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -455,142 +455,142 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46262.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
       <c r="B7">
-        <v>3.033</v>
+        <v>4.092</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1.683</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46262.0625</v>
+        <v>46269.0625</v>
       </c>
       <c r="B8">
-        <v>0.82</v>
+        <v>3.571</v>
       </c>
       <c r="C8">
-        <v>1.053</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46262.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.257</v>
+        <v>0.914</v>
       </c>
       <c r="C9">
-        <v>3.181</v>
+        <v>2.145</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46262.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.158</v>
+        <v>0.768</v>
       </c>
       <c r="C10">
-        <v>9.577</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46262.09375</v>
+        <v>46269.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>5.084</v>
       </c>
       <c r="C11">
-        <v>11.815</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46262.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="C12">
-        <v>14.316</v>
+        <v>4.397</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46262.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.09</v>
+        <v>0.782</v>
       </c>
       <c r="C13">
-        <v>7.115</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46262.125</v>
+        <v>46269.125</v>
       </c>
       <c r="B14">
-        <v>0.272</v>
+        <v>9.9</v>
       </c>
       <c r="C14">
-        <v>2.307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46262.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.318</v>
+        <v>11.49</v>
       </c>
       <c r="C15">
-        <v>0.156</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46262.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.011</v>
+        <v>3.687</v>
       </c>
       <c r="C16">
-        <v>6.384</v>
+        <v>2.247</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46262.15625</v>
+        <v>46269.15625</v>
       </c>
       <c r="B17">
-        <v>1.712</v>
+        <v>2.135</v>
       </c>
       <c r="C17">
-        <v>0.213</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46262.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
       <c r="B18">
-        <v>3.109</v>
+        <v>8.403</v>
       </c>
       <c r="C18">
-        <v>0.048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46262.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
       <c r="B19">
-        <v>15.287</v>
+        <v>4.773</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,32 +598,32 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46262.1875</v>
+        <v>46269.1875</v>
       </c>
       <c r="B20">
-        <v>25.288</v>
+        <v>0.229</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>5.547</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46262.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
       <c r="B21">
-        <v>28.898</v>
+        <v>0.947</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>3.407</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46262.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
       <c r="B22">
-        <v>14.297</v>
+        <v>1.678</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -631,342 +631,298 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46262.21875</v>
+        <v>46269.21875</v>
       </c>
       <c r="B23">
-        <v>3.872</v>
+        <v>1.841</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46262.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.19</v>
+        <v>1.465</v>
       </c>
       <c r="C24">
-        <v>2.807</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46262.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>3.735</v>
       </c>
       <c r="C25">
-        <v>6.836</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46262.25</v>
+        <v>46269.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="C26">
-        <v>18.986</v>
+        <v>5.117</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46262.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.001</v>
+        <v>1.597</v>
       </c>
       <c r="C27">
-        <v>13.233</v>
+        <v>3.013</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46262.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.268</v>
+        <v>3.756</v>
       </c>
       <c r="C28">
-        <v>3.245</v>
+        <v>3.075</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46262.28125</v>
+        <v>46269.28125</v>
       </c>
       <c r="B29">
-        <v>1.28</v>
+        <v>10.575</v>
       </c>
       <c r="C29">
-        <v>0.761</v>
+        <v>2.613</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46262.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
       <c r="B30">
-        <v>21.089</v>
+        <v>1.501</v>
       </c>
       <c r="C30">
-        <v>0.348</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46262.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
       <c r="B31">
-        <v>12.59</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>10.941</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46262.3125</v>
+        <v>46269.3125</v>
       </c>
       <c r="B32">
-        <v>3.523</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>12.667</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46262.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.852</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>10.381</v>
+        <v>53.807</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46262.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>26.787</v>
+        <v>81.405</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46262.34375</v>
+        <v>46269.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>30.769</v>
+        <v>38.285</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46262.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.447</v>
+        <v>4.808</v>
       </c>
       <c r="C36">
-        <v>16.06</v>
+        <v>1.779</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46262.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="C37">
-        <v>55.446</v>
+        <v>4.058</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46262.375</v>
+        <v>46269.375</v>
       </c>
       <c r="B38">
-        <v>1.236</v>
+        <v>33.466</v>
       </c>
       <c r="C38">
-        <v>23.365</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46262.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.054</v>
+        <v>2.227</v>
       </c>
       <c r="C39">
-        <v>6.571</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46262.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
       <c r="B40">
-        <v>1.431</v>
+        <v>0.237</v>
       </c>
       <c r="C40">
-        <v>1.701</v>
+        <v>13.624</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46262.40625</v>
+        <v>46269.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.228</v>
+        <v>29.993</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46262.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
       <c r="B42">
-        <v>2.351</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>4.601</v>
+        <v>40.437</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46262.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>10.211</v>
+        <v>25.414</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46262.4375</v>
+        <v>46269.4375</v>
       </c>
       <c r="B44">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>21.765</v>
+        <v>23.658</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46262.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>39.855</v>
+        <v>17.522</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46262.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>34.695</v>
+        <v>11.186</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46262.46875</v>
+        <v>46269.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>17.602</v>
+        <v>9.417999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46262.47916666666</v>
+        <v>46269.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>15.776</v>
+        <v>6.034</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>46262.48958333334</v>
+        <v>46269.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>10.001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46262.5</v>
-      </c>
-      <c r="B50">
-        <v>6.636</v>
-      </c>
-      <c r="C50">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46262.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0.324</v>
-      </c>
-      <c r="C51">
-        <v>12.982</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46262.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0.544</v>
-      </c>
-      <c r="C52">
-        <v>8.667999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46262.53125</v>
-      </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
         <v>0</v>
       </c>
     </row>
